--- a/data/nzd0037/nzd0037.xlsx
+++ b/data/nzd0037/nzd0037.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N485"/>
+  <dimension ref="A1:N486"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23730,6 +23730,54 @@
         <v>354.77</v>
       </c>
       <c r="N485" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-20 22:17:54+00:00</t>
+        </is>
+      </c>
+      <c r="B486" t="n">
+        <v>351.75</v>
+      </c>
+      <c r="C486" t="n">
+        <v>344.37</v>
+      </c>
+      <c r="D486" t="n">
+        <v>340.85</v>
+      </c>
+      <c r="E486" t="n">
+        <v>337.58</v>
+      </c>
+      <c r="F486" t="n">
+        <v>320.13</v>
+      </c>
+      <c r="G486" t="n">
+        <v>322.62</v>
+      </c>
+      <c r="H486" t="n">
+        <v>347.57</v>
+      </c>
+      <c r="I486" t="n">
+        <v>367.95</v>
+      </c>
+      <c r="J486" t="n">
+        <v>377.62</v>
+      </c>
+      <c r="K486" t="n">
+        <v>330.49</v>
+      </c>
+      <c r="L486" t="n">
+        <v>344.85</v>
+      </c>
+      <c r="M486" t="n">
+        <v>353.51</v>
+      </c>
+      <c r="N486" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -23746,7 +23794,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B526"/>
+  <dimension ref="A1:B527"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29009,6 +29057,16 @@
       </c>
       <c r="B526" t="n">
         <v>-0.23</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>2025-11-20 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B527" t="n">
+        <v>0.42</v>
       </c>
     </row>
   </sheetData>
@@ -29177,28 +29235,28 @@
         <v>0.0529</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3341722656077474</v>
+        <v>0.3291759666360616</v>
       </c>
       <c r="J2" t="n">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="K2" t="n">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1116233034083111</v>
+        <v>0.1084484299036786</v>
       </c>
       <c r="M2" t="n">
-        <v>5.814945570757282</v>
+        <v>5.82830596649311</v>
       </c>
       <c r="N2" t="n">
-        <v>52.44164557703874</v>
+        <v>52.67830229568118</v>
       </c>
       <c r="O2" t="n">
-        <v>7.241660415749881</v>
+        <v>7.257981971297613</v>
       </c>
       <c r="P2" t="n">
-        <v>355.9249129274029</v>
+        <v>355.9744991605602</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -29255,28 +29313,28 @@
         <v>0.0581</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4099004432715758</v>
+        <v>0.404705804427038</v>
       </c>
       <c r="J3" t="n">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="K3" t="n">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1721725039381742</v>
+        <v>0.1680728135424472</v>
       </c>
       <c r="M3" t="n">
-        <v>5.5720289789157</v>
+        <v>5.586699522502487</v>
       </c>
       <c r="N3" t="n">
-        <v>47.66790286375364</v>
+        <v>47.94231970314989</v>
       </c>
       <c r="O3" t="n">
-        <v>6.904194584725552</v>
+        <v>6.924039262103435</v>
       </c>
       <c r="P3" t="n">
-        <v>347.0704989717738</v>
+        <v>347.1220536474192</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -29333,28 +29391,28 @@
         <v>0.043</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4050384947071019</v>
+        <v>0.3995695588756282</v>
       </c>
       <c r="J4" t="n">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="K4" t="n">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1739351246401373</v>
+        <v>0.1694020773137647</v>
       </c>
       <c r="M4" t="n">
-        <v>5.422056205194647</v>
+        <v>5.439129976588686</v>
       </c>
       <c r="N4" t="n">
-        <v>45.9740413558257</v>
+        <v>46.29234999839993</v>
       </c>
       <c r="O4" t="n">
-        <v>6.780416016427436</v>
+        <v>6.803848175731138</v>
       </c>
       <c r="P4" t="n">
-        <v>344.3918485577866</v>
+        <v>344.4461255193532</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -29411,28 +29469,28 @@
         <v>0.031</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4742526066696745</v>
+        <v>0.4683800251783987</v>
       </c>
       <c r="J5" t="n">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="K5" t="n">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1505644045888579</v>
+        <v>0.1471433966408056</v>
       </c>
       <c r="M5" t="n">
-        <v>7.054451439179468</v>
+        <v>7.071556056527811</v>
       </c>
       <c r="N5" t="n">
-        <v>74.87223824933878</v>
+        <v>75.19419273479414</v>
       </c>
       <c r="O5" t="n">
-        <v>8.652874565676933</v>
+        <v>8.671458512545287</v>
       </c>
       <c r="P5" t="n">
-        <v>340.3437713946635</v>
+        <v>340.402054375068</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -29489,28 +29547,28 @@
         <v>0.0508</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4026727056217655</v>
+        <v>0.3969444450670679</v>
       </c>
       <c r="J6" t="n">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="K6" t="n">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1196067049641831</v>
+        <v>0.1164001038822595</v>
       </c>
       <c r="M6" t="n">
-        <v>6.717707779586291</v>
+        <v>6.734232811413674</v>
       </c>
       <c r="N6" t="n">
-        <v>70.42369432386995</v>
+        <v>70.73169674877195</v>
       </c>
       <c r="O6" t="n">
-        <v>8.391882644786564</v>
+        <v>8.4102138349017</v>
       </c>
       <c r="P6" t="n">
-        <v>324.3992023847491</v>
+        <v>324.4560530386152</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -29567,28 +29625,28 @@
         <v>0.0368</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2316834476695543</v>
+        <v>0.2263507489750383</v>
       </c>
       <c r="J7" t="n">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="K7" t="n">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03556588567556984</v>
+        <v>0.03399266045589533</v>
       </c>
       <c r="M7" t="n">
-        <v>7.257525271472027</v>
+        <v>7.27077984882359</v>
       </c>
       <c r="N7" t="n">
-        <v>85.88595882179344</v>
+        <v>86.10164964148899</v>
       </c>
       <c r="O7" t="n">
-        <v>9.267467767507661</v>
+        <v>9.279097458346312</v>
       </c>
       <c r="P7" t="n">
-        <v>330.3715959954295</v>
+        <v>330.4245208588779</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -29645,28 +29703,28 @@
         <v>0.0357</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2644801908111531</v>
+        <v>0.2615297559212204</v>
       </c>
       <c r="J8" t="n">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="K8" t="n">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1382670715840326</v>
+        <v>0.1355684837252071</v>
       </c>
       <c r="M8" t="n">
-        <v>3.727334171502394</v>
+        <v>3.737135081219733</v>
       </c>
       <c r="N8" t="n">
-        <v>25.72370027918876</v>
+        <v>25.79089428760784</v>
       </c>
       <c r="O8" t="n">
-        <v>5.071853732038096</v>
+        <v>5.078473617890305</v>
       </c>
       <c r="P8" t="n">
-        <v>348.2670449603942</v>
+        <v>348.29632682547</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -29723,28 +29781,28 @@
         <v>0.0322</v>
       </c>
       <c r="I9" t="n">
-        <v>0.17603028678629</v>
+        <v>0.1752437310868669</v>
       </c>
       <c r="J9" t="n">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="K9" t="n">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03836783461680005</v>
+        <v>0.0381885178587803</v>
       </c>
       <c r="M9" t="n">
-        <v>4.790982846374598</v>
+        <v>4.785932594782965</v>
       </c>
       <c r="N9" t="n">
-        <v>45.82576283531154</v>
+        <v>45.73982166620944</v>
       </c>
       <c r="O9" t="n">
-        <v>6.769472862439994</v>
+        <v>6.763122183297403</v>
       </c>
       <c r="P9" t="n">
-        <v>365.3533163747764</v>
+        <v>365.3611226198637</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -29801,28 +29859,28 @@
         <v>0.0257</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1352818902558441</v>
+        <v>0.1322146295373081</v>
       </c>
       <c r="J10" t="n">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="K10" t="n">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02024598986250148</v>
+        <v>0.01938977555145716</v>
       </c>
       <c r="M10" t="n">
-        <v>5.584403753055997</v>
+        <v>5.593082355552338</v>
       </c>
       <c r="N10" t="n">
-        <v>52.25773455012987</v>
+        <v>52.27992920732051</v>
       </c>
       <c r="O10" t="n">
-        <v>7.228951137622239</v>
+        <v>7.23048609758158</v>
       </c>
       <c r="P10" t="n">
-        <v>382.0232871419845</v>
+        <v>382.0537284558461</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -29883,28 +29941,28 @@
         <v>0.0708</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6426400935230535</v>
+        <v>0.6369167819069321</v>
       </c>
       <c r="J11" t="n">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="K11" t="n">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3720731243237214</v>
+        <v>0.3663480385131993</v>
       </c>
       <c r="M11" t="n">
-        <v>4.99090930863589</v>
+        <v>5.011595846402176</v>
       </c>
       <c r="N11" t="n">
-        <v>41.12535148781771</v>
+        <v>41.49298010954745</v>
       </c>
       <c r="O11" t="n">
-        <v>6.412905073975266</v>
+        <v>6.441504491153247</v>
       </c>
       <c r="P11" t="n">
-        <v>328.4287587373917</v>
+        <v>328.4855602750573</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -29961,28 +30019,28 @@
         <v>0.07340000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6690616349716529</v>
+        <v>0.6643419095697785</v>
       </c>
       <c r="J12" t="n">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="K12" t="n">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="L12" t="n">
-        <v>0.4363622984267983</v>
+        <v>0.4317239747393286</v>
       </c>
       <c r="M12" t="n">
-        <v>4.66596828771854</v>
+        <v>4.681729711868267</v>
       </c>
       <c r="N12" t="n">
-        <v>34.11758542207237</v>
+        <v>34.35490872080954</v>
       </c>
       <c r="O12" t="n">
-        <v>5.841026059013294</v>
+        <v>5.861306059301932</v>
       </c>
       <c r="P12" t="n">
-        <v>339.4957492794091</v>
+        <v>339.542590632487</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -30039,28 +30097,28 @@
         <v>0.0422</v>
       </c>
       <c r="I13" t="n">
-        <v>0.558971569349237</v>
+        <v>0.5563164392660978</v>
       </c>
       <c r="J13" t="n">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="K13" t="n">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="L13" t="n">
-        <v>0.3874517783855541</v>
+        <v>0.3854145511360406</v>
       </c>
       <c r="M13" t="n">
-        <v>4.23082024075344</v>
+        <v>4.237074523272784</v>
       </c>
       <c r="N13" t="n">
-        <v>29.14709530845262</v>
+        <v>29.18436741584625</v>
       </c>
       <c r="O13" t="n">
-        <v>5.398804988926033</v>
+        <v>5.402255771050298</v>
       </c>
       <c r="P13" t="n">
-        <v>345.6862312118136</v>
+        <v>345.7125822969091</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -30098,7 +30156,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N485"/>
+  <dimension ref="A1:N486"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65021,6 +65079,78 @@
         </is>
       </c>
     </row>
+    <row r="486">
+      <c r="A486" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-20 22:17:54+00:00</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>-34.964090596209,173.64159278381655</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>-34.96452414854586,173.6423238465364</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>-34.964930541892564,173.64308261169748</t>
+        </is>
+      </c>
+      <c r="E486" t="inlineStr">
+        <is>
+          <t>-34.96530483176267,173.6438860716808</t>
+        </is>
+      </c>
+      <c r="F486" t="inlineStr">
+        <is>
+          <t>-34.96569588398,173.64469703217287</t>
+        </is>
+      </c>
+      <c r="G486" t="inlineStr">
+        <is>
+          <t>-34.96592334249995,173.6456200512356</t>
+        </is>
+      </c>
+      <c r="H486" t="inlineStr">
+        <is>
+          <t>-34.96572784039848,173.64658798953104</t>
+        </is>
+      </c>
+      <c r="I486" t="inlineStr">
+        <is>
+          <t>-34.96551393676387,173.64748227931136</t>
+        </is>
+      </c>
+      <c r="J486" t="inlineStr">
+        <is>
+          <t>-34.96541100855762,173.6483813283279</t>
+        </is>
+      </c>
+      <c r="K486" t="inlineStr">
+        <is>
+          <t>-34.96585178012419,173.6492705387324</t>
+        </is>
+      </c>
+      <c r="L486" t="inlineStr">
+        <is>
+          <t>-34.96574778930359,173.65021971702592</t>
+        </is>
+      </c>
+      <c r="M486" t="inlineStr">
+        <is>
+          <t>-34.96534984018927,173.65102675603043</t>
+        </is>
+      </c>
+      <c r="N486" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0037/nzd0037.xlsx
+++ b/data/nzd0037/nzd0037.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N486"/>
+  <dimension ref="A1:N488"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23780,6 +23780,102 @@
       <c r="N486" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:17:51+00:00</t>
+        </is>
+      </c>
+      <c r="B487" t="n">
+        <v>351.39</v>
+      </c>
+      <c r="C487" t="n">
+        <v>343.85</v>
+      </c>
+      <c r="D487" t="n">
+        <v>339.94</v>
+      </c>
+      <c r="E487" t="n">
+        <v>338.01</v>
+      </c>
+      <c r="F487" t="n">
+        <v>320.99</v>
+      </c>
+      <c r="G487" t="n">
+        <v>323.74</v>
+      </c>
+      <c r="H487" t="n">
+        <v>348.1</v>
+      </c>
+      <c r="I487" t="n">
+        <v>368.93</v>
+      </c>
+      <c r="J487" t="n">
+        <v>380.14</v>
+      </c>
+      <c r="K487" t="n">
+        <v>332.26</v>
+      </c>
+      <c r="L487" t="n">
+        <v>346.23</v>
+      </c>
+      <c r="M487" t="n">
+        <v>354.74</v>
+      </c>
+      <c r="N487" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-14 22:17:57+00:00</t>
+        </is>
+      </c>
+      <c r="B488" t="n">
+        <v>350.75</v>
+      </c>
+      <c r="C488" t="n">
+        <v>342.95</v>
+      </c>
+      <c r="D488" t="n">
+        <v>338.97</v>
+      </c>
+      <c r="E488" t="n">
+        <v>337.5</v>
+      </c>
+      <c r="F488" t="n">
+        <v>320.04</v>
+      </c>
+      <c r="G488" t="n">
+        <v>323.37</v>
+      </c>
+      <c r="H488" t="n">
+        <v>346.89</v>
+      </c>
+      <c r="I488" t="n">
+        <v>368.93</v>
+      </c>
+      <c r="J488" t="n">
+        <v>381.54</v>
+      </c>
+      <c r="K488" t="n">
+        <v>332.66</v>
+      </c>
+      <c r="L488" t="n">
+        <v>346.56</v>
+      </c>
+      <c r="M488" t="n">
+        <v>355</v>
+      </c>
+      <c r="N488" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -23794,7 +23890,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B527"/>
+  <dimension ref="A1:B529"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29067,6 +29163,26 @@
       </c>
       <c r="B527" t="n">
         <v>0.42</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B528" t="n">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>2025-12-14 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B529" t="n">
+        <v>-0.49</v>
       </c>
     </row>
   </sheetData>
@@ -29235,28 +29351,28 @@
         <v>0.0529</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3291759666360616</v>
+        <v>0.3187883161328227</v>
       </c>
       <c r="J2" t="n">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="K2" t="n">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1084484299036786</v>
+        <v>0.1018827485806857</v>
       </c>
       <c r="M2" t="n">
-        <v>5.82830596649311</v>
+        <v>5.857161142486506</v>
       </c>
       <c r="N2" t="n">
-        <v>52.67830229568118</v>
+        <v>53.21123050584605</v>
       </c>
       <c r="O2" t="n">
-        <v>7.257981971297613</v>
+        <v>7.294602834003099</v>
       </c>
       <c r="P2" t="n">
-        <v>355.9744991605602</v>
+        <v>356.0778679590545</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -29313,28 +29429,28 @@
         <v>0.0581</v>
       </c>
       <c r="I3" t="n">
-        <v>0.404705804427038</v>
+        <v>0.393701612299028</v>
       </c>
       <c r="J3" t="n">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="K3" t="n">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1680728135424472</v>
+        <v>0.1593027312017018</v>
       </c>
       <c r="M3" t="n">
-        <v>5.586699522502487</v>
+        <v>5.619236791018199</v>
       </c>
       <c r="N3" t="n">
-        <v>47.94231970314989</v>
+        <v>48.58664667723582</v>
       </c>
       <c r="O3" t="n">
-        <v>6.924039262103435</v>
+        <v>6.970412231513701</v>
       </c>
       <c r="P3" t="n">
-        <v>347.1220536474192</v>
+        <v>347.231558202163</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -29391,28 +29507,28 @@
         <v>0.043</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3995695588756282</v>
+        <v>0.3876962755246216</v>
       </c>
       <c r="J4" t="n">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="K4" t="n">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1694020773137647</v>
+        <v>0.1593998702932213</v>
       </c>
       <c r="M4" t="n">
-        <v>5.439129976588686</v>
+        <v>5.477975888451417</v>
       </c>
       <c r="N4" t="n">
-        <v>46.29234999839993</v>
+        <v>47.08156295707039</v>
       </c>
       <c r="O4" t="n">
-        <v>6.803848175731138</v>
+        <v>6.861600611888628</v>
       </c>
       <c r="P4" t="n">
-        <v>344.4461255193532</v>
+        <v>344.564278533006</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -29469,28 +29585,28 @@
         <v>0.031</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4683800251783987</v>
+        <v>0.4569122471099514</v>
       </c>
       <c r="J5" t="n">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="K5" t="n">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1471433966408056</v>
+        <v>0.1405949980965406</v>
       </c>
       <c r="M5" t="n">
-        <v>7.071556056527811</v>
+        <v>7.104584076339485</v>
       </c>
       <c r="N5" t="n">
-        <v>75.19419273479414</v>
+        <v>75.79834613822555</v>
       </c>
       <c r="O5" t="n">
-        <v>8.671458512545287</v>
+        <v>8.706224562818578</v>
       </c>
       <c r="P5" t="n">
-        <v>340.402054375068</v>
+        <v>340.5161712674984</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -29547,28 +29663,28 @@
         <v>0.0508</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3969444450670679</v>
+        <v>0.3859275328397344</v>
       </c>
       <c r="J6" t="n">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="K6" t="n">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1164001038822595</v>
+        <v>0.1104018946603418</v>
       </c>
       <c r="M6" t="n">
-        <v>6.734232811413674</v>
+        <v>6.764806301186565</v>
       </c>
       <c r="N6" t="n">
-        <v>70.73169674877195</v>
+        <v>71.28447799709741</v>
       </c>
       <c r="O6" t="n">
-        <v>8.4102138349017</v>
+        <v>8.443013561347477</v>
       </c>
       <c r="P6" t="n">
-        <v>324.4560530386152</v>
+        <v>324.5656842811807</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -29625,28 +29741,28 @@
         <v>0.0368</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2263507489750383</v>
+        <v>0.2165331327111638</v>
       </c>
       <c r="J7" t="n">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="K7" t="n">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03399266045589533</v>
+        <v>0.03122051072200727</v>
       </c>
       <c r="M7" t="n">
-        <v>7.27077984882359</v>
+        <v>7.292401738064335</v>
       </c>
       <c r="N7" t="n">
-        <v>86.10164964148899</v>
+        <v>86.41711735581883</v>
       </c>
       <c r="O7" t="n">
-        <v>9.279097458346312</v>
+        <v>9.296080752436417</v>
       </c>
       <c r="P7" t="n">
-        <v>330.4245208588779</v>
+        <v>330.5222167039304</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -29703,28 +29819,28 @@
         <v>0.0357</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2615297559212204</v>
+        <v>0.2556440183659857</v>
       </c>
       <c r="J8" t="n">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="K8" t="n">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1355684837252071</v>
+        <v>0.1302249349143817</v>
       </c>
       <c r="M8" t="n">
-        <v>3.737135081219733</v>
+        <v>3.757524846347125</v>
       </c>
       <c r="N8" t="n">
-        <v>25.79089428760784</v>
+        <v>25.92687654073734</v>
       </c>
       <c r="O8" t="n">
-        <v>5.078473617890305</v>
+        <v>5.091844119838837</v>
       </c>
       <c r="P8" t="n">
-        <v>348.29632682547</v>
+        <v>348.3548982608548</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -29781,28 +29897,28 @@
         <v>0.0322</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1752437310868669</v>
+        <v>0.1744356762838876</v>
       </c>
       <c r="J9" t="n">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="K9" t="n">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0381885178587803</v>
+        <v>0.03815837500428099</v>
       </c>
       <c r="M9" t="n">
-        <v>4.785932594782965</v>
+        <v>4.771197601922387</v>
       </c>
       <c r="N9" t="n">
-        <v>45.73982166620944</v>
+        <v>45.55651013980152</v>
       </c>
       <c r="O9" t="n">
-        <v>6.763122183297403</v>
+        <v>6.749556292068503</v>
       </c>
       <c r="P9" t="n">
-        <v>365.3611226198637</v>
+        <v>365.3691635804672</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -29859,28 +29975,28 @@
         <v>0.0257</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1322146295373081</v>
+        <v>0.1286222814540683</v>
       </c>
       <c r="J10" t="n">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="K10" t="n">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01938977555145716</v>
+        <v>0.01849189739752355</v>
       </c>
       <c r="M10" t="n">
-        <v>5.593082355552338</v>
+        <v>5.593952318360895</v>
       </c>
       <c r="N10" t="n">
-        <v>52.27992920732051</v>
+        <v>52.15680217702462</v>
       </c>
       <c r="O10" t="n">
-        <v>7.23048609758158</v>
+        <v>7.221966641921342</v>
       </c>
       <c r="P10" t="n">
-        <v>382.0537284558461</v>
+        <v>382.0894730791901</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -29941,28 +30057,28 @@
         <v>0.0708</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6369167819069321</v>
+        <v>0.627110326699244</v>
       </c>
       <c r="J11" t="n">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="K11" t="n">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3663480385131993</v>
+        <v>0.3574489413630655</v>
       </c>
       <c r="M11" t="n">
-        <v>5.011595846402176</v>
+        <v>5.044214044786684</v>
       </c>
       <c r="N11" t="n">
-        <v>41.49298010954745</v>
+        <v>41.99017241409511</v>
       </c>
       <c r="O11" t="n">
-        <v>6.441504491153247</v>
+        <v>6.479982439335396</v>
       </c>
       <c r="P11" t="n">
-        <v>328.4855602750573</v>
+        <v>328.5831435193873</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -30019,28 +30135,28 @@
         <v>0.07340000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6643419095697785</v>
+        <v>0.656183345632192</v>
       </c>
       <c r="J12" t="n">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="K12" t="n">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="L12" t="n">
-        <v>0.4317239747393286</v>
+        <v>0.4244755386858479</v>
       </c>
       <c r="M12" t="n">
-        <v>4.681729711868267</v>
+        <v>4.706411999568736</v>
       </c>
       <c r="N12" t="n">
-        <v>34.35490872080954</v>
+        <v>34.67589272095899</v>
       </c>
       <c r="O12" t="n">
-        <v>5.861306059301932</v>
+        <v>5.888624009134816</v>
       </c>
       <c r="P12" t="n">
-        <v>339.542590632487</v>
+        <v>339.6237758647103</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -30097,28 +30213,28 @@
         <v>0.0422</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5563164392660978</v>
+        <v>0.5520982790515688</v>
       </c>
       <c r="J13" t="n">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="K13" t="n">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="L13" t="n">
-        <v>0.3854145511360406</v>
+        <v>0.3828258511505384</v>
       </c>
       <c r="M13" t="n">
-        <v>4.237074523272784</v>
+        <v>4.243340344708702</v>
       </c>
       <c r="N13" t="n">
-        <v>29.18436741584625</v>
+        <v>29.18807016545414</v>
       </c>
       <c r="O13" t="n">
-        <v>5.402255771050298</v>
+        <v>5.402598464207213</v>
       </c>
       <c r="P13" t="n">
-        <v>345.7125822969091</v>
+        <v>345.7545566995547</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -30156,7 +30272,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N486"/>
+  <dimension ref="A1:N488"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65151,6 +65267,150 @@
         </is>
       </c>
     </row>
+    <row r="487">
+      <c r="A487" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:17:51+00:00</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>-34.964093392112886,173.64159078023656</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>-34.964528187084106,173.64232095248423</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>-34.9649377255503,173.6430777943982</t>
+        </is>
+      </c>
+      <c r="E487" t="inlineStr">
+        <is>
+          <t>-34.96530125859323,173.643887900431</t>
+        </is>
+      </c>
+      <c r="F487" t="inlineStr">
+        <is>
+          <t>-34.96568852809102,173.64470001428248</t>
+        </is>
+      </c>
+      <c r="G487" t="inlineStr">
+        <is>
+          <t>-34.96591339936947,173.64562219940777</t>
+        </is>
+      </c>
+      <c r="H487" t="inlineStr">
+        <is>
+          <t>-34.96572306151452,173.64658793888594</t>
+        </is>
+      </c>
+      <c r="I487" t="inlineStr">
+        <is>
+          <t>-34.96550510553927,173.6474818993348</t>
+        </is>
+      </c>
+      <c r="J487" t="inlineStr">
+        <is>
+          <t>-34.96538828563681,173.64838121833893</t>
+        </is>
+      </c>
+      <c r="K487" t="inlineStr">
+        <is>
+          <t>-34.9658358252078,173.64927104088045</t>
+        </is>
+      </c>
+      <c r="L487" t="inlineStr">
+        <is>
+          <t>-34.965735614336154,173.65021659308582</t>
+        </is>
+      </c>
+      <c r="M487" t="inlineStr">
+        <is>
+          <t>-34.96533986894456,173.65102085658472</t>
+        </is>
+      </c>
+      <c r="N487" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-14 22:17:57+00:00</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>-34.96409836260859,173.6415872183162</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>-34.96453517686164,173.64231594354706</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>-34.9649453828556,173.64307265947392</t>
+        </is>
+      </c>
+      <c r="E488" t="inlineStr">
+        <is>
+          <t>-34.965305496538384,173.6438857314482</t>
+        </is>
+      </c>
+      <c r="F488" t="inlineStr">
+        <is>
+          <t>-34.965696653782324,173.64469672009162</t>
+        </is>
+      </c>
+      <c r="G488" t="inlineStr">
+        <is>
+          <t>-34.96591668415365,173.6456214897438</t>
+        </is>
+      </c>
+      <c r="H488" t="inlineStr">
+        <is>
+          <t>-34.965733971796766,173.64658805450966</t>
+        </is>
+      </c>
+      <c r="I488" t="inlineStr">
+        <is>
+          <t>-34.96550510553927,173.6474818993348</t>
+        </is>
+      </c>
+      <c r="J488" t="inlineStr">
+        <is>
+          <t>-34.96537566179189,173.648381157234</t>
+        </is>
+      </c>
+      <c r="K488" t="inlineStr">
+        <is>
+          <t>-34.965832219576974,173.64927115436024</t>
+        </is>
+      </c>
+      <c r="L488" t="inlineStr">
+        <is>
+          <t>-34.96573270293087,173.6502158460568</t>
+        </is>
+      </c>
+      <c r="M488" t="inlineStr">
+        <is>
+          <t>-34.96533776120174,173.6510196095476</t>
+        </is>
+      </c>
+      <c r="N488" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0037/nzd0037.xlsx
+++ b/data/nzd0037/nzd0037.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N488"/>
+  <dimension ref="A1:N490"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23874,6 +23874,102 @@
         <v>355</v>
       </c>
       <c r="N488" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:18:00+00:00</t>
+        </is>
+      </c>
+      <c r="B489" t="n">
+        <v>350.29</v>
+      </c>
+      <c r="C489" t="n">
+        <v>342.34</v>
+      </c>
+      <c r="D489" t="n">
+        <v>337.75</v>
+      </c>
+      <c r="E489" t="n">
+        <v>333.77</v>
+      </c>
+      <c r="F489" t="n">
+        <v>320.55</v>
+      </c>
+      <c r="G489" t="n">
+        <v>322.52</v>
+      </c>
+      <c r="H489" t="n">
+        <v>343.61</v>
+      </c>
+      <c r="I489" t="n">
+        <v>370.16</v>
+      </c>
+      <c r="J489" t="n">
+        <v>383.39</v>
+      </c>
+      <c r="K489" t="n">
+        <v>332.55</v>
+      </c>
+      <c r="L489" t="n">
+        <v>347.04</v>
+      </c>
+      <c r="M489" t="n">
+        <v>352.99</v>
+      </c>
+      <c r="N489" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:11:42+00:00</t>
+        </is>
+      </c>
+      <c r="B490" t="n">
+        <v>351.32</v>
+      </c>
+      <c r="C490" t="n">
+        <v>343.2</v>
+      </c>
+      <c r="D490" t="n">
+        <v>338.86</v>
+      </c>
+      <c r="E490" t="n">
+        <v>335.37</v>
+      </c>
+      <c r="F490" t="n">
+        <v>321.6</v>
+      </c>
+      <c r="G490" t="n">
+        <v>324.04</v>
+      </c>
+      <c r="H490" t="n">
+        <v>344.97</v>
+      </c>
+      <c r="I490" t="n">
+        <v>370.64</v>
+      </c>
+      <c r="J490" t="n">
+        <v>383.44</v>
+      </c>
+      <c r="K490" t="n">
+        <v>333.49</v>
+      </c>
+      <c r="L490" t="n">
+        <v>347.9</v>
+      </c>
+      <c r="M490" t="n">
+        <v>354.06</v>
+      </c>
+      <c r="N490" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -23890,7 +23986,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B529"/>
+  <dimension ref="A1:B531"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29183,6 +29279,26 @@
       </c>
       <c r="B529" t="n">
         <v>-0.49</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B530" t="n">
+        <v>-0.64</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B531" t="n">
+        <v>0.6</v>
       </c>
     </row>
   </sheetData>
@@ -29351,28 +29467,28 @@
         <v>0.0529</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3187883161328227</v>
+        <v>0.3083805164791377</v>
       </c>
       <c r="J2" t="n">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="K2" t="n">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1018827485806857</v>
+        <v>0.09546895477646555</v>
       </c>
       <c r="M2" t="n">
-        <v>5.857161142486506</v>
+        <v>5.886278268670401</v>
       </c>
       <c r="N2" t="n">
-        <v>53.21123050584605</v>
+        <v>53.75332893197375</v>
       </c>
       <c r="O2" t="n">
-        <v>7.294602834003099</v>
+        <v>7.331666177068739</v>
       </c>
       <c r="P2" t="n">
-        <v>356.0778679590545</v>
+        <v>356.1817708534056</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -29429,28 +29545,28 @@
         <v>0.0581</v>
       </c>
       <c r="I3" t="n">
-        <v>0.393701612299028</v>
+        <v>0.3824043567151053</v>
       </c>
       <c r="J3" t="n">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="K3" t="n">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1593027312017018</v>
+        <v>0.1503969343054059</v>
       </c>
       <c r="M3" t="n">
-        <v>5.619236791018199</v>
+        <v>5.653716807183946</v>
       </c>
       <c r="N3" t="n">
-        <v>48.58664667723582</v>
+        <v>49.28252410636739</v>
       </c>
       <c r="O3" t="n">
-        <v>6.970412231513701</v>
+        <v>7.020151287997104</v>
       </c>
       <c r="P3" t="n">
-        <v>347.231558202163</v>
+        <v>347.34434128356</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -29507,28 +29623,28 @@
         <v>0.043</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3876962755246216</v>
+        <v>0.3751582539442969</v>
       </c>
       <c r="J4" t="n">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="K4" t="n">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1593998702932213</v>
+        <v>0.1489067164083642</v>
       </c>
       <c r="M4" t="n">
-        <v>5.477975888451417</v>
+        <v>5.521270109628059</v>
       </c>
       <c r="N4" t="n">
-        <v>47.08156295707039</v>
+        <v>47.99125210394082</v>
       </c>
       <c r="O4" t="n">
-        <v>6.861600611888628</v>
+        <v>6.927571876490407</v>
       </c>
       <c r="P4" t="n">
-        <v>344.564278533006</v>
+        <v>344.6894480871663</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -29585,28 +29701,28 @@
         <v>0.031</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4569122471099514</v>
+        <v>0.4432215307464309</v>
       </c>
       <c r="J5" t="n">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="K5" t="n">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1405949980965406</v>
+        <v>0.132389745541732</v>
       </c>
       <c r="M5" t="n">
-        <v>7.104584076339485</v>
+        <v>7.150263992829651</v>
       </c>
       <c r="N5" t="n">
-        <v>75.79834613822555</v>
+        <v>76.80371376180702</v>
       </c>
       <c r="O5" t="n">
-        <v>8.706224562818578</v>
+        <v>8.763772804095678</v>
       </c>
       <c r="P5" t="n">
-        <v>340.5161712674984</v>
+        <v>340.6528475228483</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -29663,28 +29779,28 @@
         <v>0.0508</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3859275328397344</v>
+        <v>0.3755270251006755</v>
       </c>
       <c r="J6" t="n">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="K6" t="n">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1104018946603418</v>
+        <v>0.1049468851283002</v>
       </c>
       <c r="M6" t="n">
-        <v>6.764806301186565</v>
+        <v>6.791874568751255</v>
       </c>
       <c r="N6" t="n">
-        <v>71.28447799709741</v>
+        <v>71.75164159149364</v>
       </c>
       <c r="O6" t="n">
-        <v>8.443013561347477</v>
+        <v>8.470634072576482</v>
       </c>
       <c r="P6" t="n">
-        <v>324.5656842811807</v>
+        <v>324.6695143281843</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -29741,28 +29857,28 @@
         <v>0.0368</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2165331327111638</v>
+        <v>0.206687320363904</v>
       </c>
       <c r="J7" t="n">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="K7" t="n">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03122051072200727</v>
+        <v>0.02854155350823961</v>
       </c>
       <c r="M7" t="n">
-        <v>7.292401738064335</v>
+        <v>7.314164866568136</v>
       </c>
       <c r="N7" t="n">
-        <v>86.41711735581883</v>
+        <v>86.74500634511601</v>
       </c>
       <c r="O7" t="n">
-        <v>9.296080752436417</v>
+        <v>9.313699927800767</v>
       </c>
       <c r="P7" t="n">
-        <v>330.5222167039304</v>
+        <v>330.6205079256414</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -29819,28 +29935,28 @@
         <v>0.0357</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2556440183659857</v>
+        <v>0.2474221353203907</v>
       </c>
       <c r="J8" t="n">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="K8" t="n">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1302249349143817</v>
+        <v>0.1219479446366729</v>
       </c>
       <c r="M8" t="n">
-        <v>3.757524846347125</v>
+        <v>3.793018443681851</v>
       </c>
       <c r="N8" t="n">
-        <v>25.92687654073734</v>
+        <v>26.29620477393376</v>
       </c>
       <c r="O8" t="n">
-        <v>5.091844119838837</v>
+        <v>5.127982524729756</v>
       </c>
       <c r="P8" t="n">
-        <v>348.3548982608548</v>
+        <v>348.4369775070269</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -29897,28 +30013,28 @@
         <v>0.0322</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1744356762838876</v>
+        <v>0.1747501586718517</v>
       </c>
       <c r="J9" t="n">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="K9" t="n">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03815837500428099</v>
+        <v>0.0386036551951241</v>
       </c>
       <c r="M9" t="n">
-        <v>4.771197601922387</v>
+        <v>4.753129996549112</v>
       </c>
       <c r="N9" t="n">
-        <v>45.55651013980152</v>
+        <v>45.3711083986882</v>
       </c>
       <c r="O9" t="n">
-        <v>6.749556292068503</v>
+        <v>6.735807924717584</v>
       </c>
       <c r="P9" t="n">
-        <v>365.3691635804672</v>
+        <v>365.3660228945072</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -29975,28 +30091,28 @@
         <v>0.0257</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1286222814540683</v>
+        <v>0.1270476113395989</v>
       </c>
       <c r="J10" t="n">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="K10" t="n">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01849189739752355</v>
+        <v>0.0181950054435146</v>
       </c>
       <c r="M10" t="n">
-        <v>5.593952318360895</v>
+        <v>5.581529383052088</v>
       </c>
       <c r="N10" t="n">
-        <v>52.15680217702462</v>
+        <v>51.96085017796307</v>
       </c>
       <c r="O10" t="n">
-        <v>7.221966641921342</v>
+        <v>7.208387488056054</v>
       </c>
       <c r="P10" t="n">
-        <v>382.0894730791901</v>
+        <v>382.1051935213328</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -30057,28 +30173,28 @@
         <v>0.0708</v>
       </c>
       <c r="I11" t="n">
-        <v>0.627110326699244</v>
+        <v>0.6178823232317071</v>
       </c>
       <c r="J11" t="n">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="K11" t="n">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3574489413630655</v>
+        <v>0.3493717515707847</v>
       </c>
       <c r="M11" t="n">
-        <v>5.044214044786684</v>
+        <v>5.073639787626837</v>
       </c>
       <c r="N11" t="n">
-        <v>41.99017241409511</v>
+        <v>42.41572184857839</v>
       </c>
       <c r="O11" t="n">
-        <v>6.479982439335396</v>
+        <v>6.512735358401906</v>
       </c>
       <c r="P11" t="n">
-        <v>328.5831435193873</v>
+        <v>328.6752682580149</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -30135,28 +30251,28 @@
         <v>0.07340000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>0.656183345632192</v>
+        <v>0.6489616116711612</v>
       </c>
       <c r="J12" t="n">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="K12" t="n">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="L12" t="n">
-        <v>0.4244755386858479</v>
+        <v>0.4185762262029216</v>
       </c>
       <c r="M12" t="n">
-        <v>4.706411999568736</v>
+        <v>4.726739792995055</v>
       </c>
       <c r="N12" t="n">
-        <v>34.67589272095899</v>
+        <v>34.90008103387724</v>
       </c>
       <c r="O12" t="n">
-        <v>5.888624009134816</v>
+        <v>5.907629053510151</v>
       </c>
       <c r="P12" t="n">
-        <v>339.6237758647103</v>
+        <v>339.6958713880879</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -30213,28 +30329,28 @@
         <v>0.0422</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5520982790515688</v>
+        <v>0.5469106112055644</v>
       </c>
       <c r="J13" t="n">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="K13" t="n">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="L13" t="n">
-        <v>0.3828258511505384</v>
+        <v>0.3788404181934857</v>
       </c>
       <c r="M13" t="n">
-        <v>4.243340344708702</v>
+        <v>4.255122107599439</v>
       </c>
       <c r="N13" t="n">
-        <v>29.18807016545414</v>
+        <v>29.2583461518905</v>
       </c>
       <c r="O13" t="n">
-        <v>5.402598464207213</v>
+        <v>5.409098460177121</v>
       </c>
       <c r="P13" t="n">
-        <v>345.7545566995547</v>
+        <v>345.8063448427328</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -30272,7 +30388,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N488"/>
+  <dimension ref="A1:N490"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65411,6 +65527,150 @@
         </is>
       </c>
     </row>
+    <row r="489">
+      <c r="A489" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:18:00+00:00</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>-34.96410193515234,173.6415846581857</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>-34.96453991437741,173.64231254860027</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>-34.964955013692894,173.64306620111415</t>
+        </is>
+      </c>
+      <c r="E489" t="inlineStr">
+        <is>
+          <t>-34.96533649170465,173.6438698680968</t>
+        </is>
+      </c>
+      <c r="F489" t="inlineStr">
+        <is>
+          <t>-34.96569229156912,173.64469848855205</t>
+        </is>
+      </c>
+      <c r="G489" t="inlineStr">
+        <is>
+          <t>-34.96592423027945,173.6456198594345</t>
+        </is>
+      </c>
+      <c r="H489" t="inlineStr">
+        <is>
+          <t>-34.965763546776664,173.6465883679363</t>
+        </is>
+      </c>
+      <c r="I489" t="inlineStr">
+        <is>
+          <t>-34.96549402145125,173.64748142242559</t>
+        </is>
+      </c>
+      <c r="J489" t="inlineStr">
+        <is>
+          <t>-34.965358980282474,173.6483810764883</t>
+        </is>
+      </c>
+      <c r="K489" t="inlineStr">
+        <is>
+          <t>-34.965833211125464,173.64927112315328</t>
+        </is>
+      </c>
+      <c r="L489" t="inlineStr">
+        <is>
+          <t>-34.965728468159554,173.65021475946924</t>
+        </is>
+      </c>
+      <c r="M489" t="inlineStr">
+        <is>
+          <t>-34.96535405567472,173.6510292501055</t>
+        </is>
+      </c>
+      <c r="N489" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:11:42+00:00</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>-34.96409393576086,173.64159039065154</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>-34.9645332352568,173.64231733491854</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>-34.964946251209795,173.64307207716286</t>
+        </is>
+      </c>
+      <c r="E490" t="inlineStr">
+        <is>
+          <t>-34.96532319619123,173.643876672753</t>
+        </is>
+      </c>
+      <c r="F490" t="inlineStr">
+        <is>
+          <t>-34.96568331054184,173.64470212949942</t>
+        </is>
+      </c>
+      <c r="G490" t="inlineStr">
+        <is>
+          <t>-34.965910736030935,173.6456227748109</t>
+        </is>
+      </c>
+      <c r="H490" t="inlineStr">
+        <is>
+          <t>-34.96575128398015,173.64658823797888</t>
+        </is>
+      </c>
+      <c r="I490" t="inlineStr">
+        <is>
+          <t>-34.96548969595346,173.64748123631472</t>
+        </is>
+      </c>
+      <c r="J490" t="inlineStr">
+        <is>
+          <t>-34.965358529430866,173.648381074306</t>
+        </is>
+      </c>
+      <c r="K490" t="inlineStr">
+        <is>
+          <t>-34.965824737892994,173.64927138983072</t>
+        </is>
+      </c>
+      <c r="L490" t="inlineStr">
+        <is>
+          <t>-34.96572088086089,173.6502128126668</t>
+        </is>
+      </c>
+      <c r="M490" t="inlineStr">
+        <is>
+          <t>-34.965345381502644,173.65102411806674</t>
+        </is>
+      </c>
+      <c r="N490" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0037/nzd0037.xlsx
+++ b/data/nzd0037/nzd0037.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N490"/>
+  <dimension ref="A1:N491"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23972,6 +23972,54 @@
       <c r="N490" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-23 22:17:42+00:00</t>
+        </is>
+      </c>
+      <c r="B491" t="n">
+        <v>351.21</v>
+      </c>
+      <c r="C491" t="n">
+        <v>342.9</v>
+      </c>
+      <c r="D491" t="n">
+        <v>338.97</v>
+      </c>
+      <c r="E491" t="n">
+        <v>334.33</v>
+      </c>
+      <c r="F491" t="n">
+        <v>320.66</v>
+      </c>
+      <c r="G491" t="n">
+        <v>323.98</v>
+      </c>
+      <c r="H491" t="n">
+        <v>345.18</v>
+      </c>
+      <c r="I491" t="n">
+        <v>369.26</v>
+      </c>
+      <c r="J491" t="n">
+        <v>381.57</v>
+      </c>
+      <c r="K491" t="n">
+        <v>333.66</v>
+      </c>
+      <c r="L491" t="n">
+        <v>348.47</v>
+      </c>
+      <c r="M491" t="n">
+        <v>353.79</v>
+      </c>
+      <c r="N491" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -23986,7 +24034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B531"/>
+  <dimension ref="A1:B532"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29299,6 +29347,16 @@
       </c>
       <c r="B531" t="n">
         <v>0.6</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>2026-01-23 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B532" t="n">
+        <v>0.84</v>
       </c>
     </row>
   </sheetData>
@@ -29467,28 +29525,28 @@
         <v>0.0529</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3083805164791377</v>
+        <v>0.3033970214221905</v>
       </c>
       <c r="J2" t="n">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="K2" t="n">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="L2" t="n">
-        <v>0.09546895477646555</v>
+        <v>0.09250033832559956</v>
       </c>
       <c r="M2" t="n">
-        <v>5.886278268670401</v>
+        <v>5.900113416724663</v>
       </c>
       <c r="N2" t="n">
-        <v>53.75332893197375</v>
+        <v>53.99399149559843</v>
       </c>
       <c r="O2" t="n">
-        <v>7.331666177068739</v>
+        <v>7.348060390034804</v>
       </c>
       <c r="P2" t="n">
-        <v>356.1817708534056</v>
+        <v>356.2316518092962</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -29545,28 +29603,28 @@
         <v>0.0581</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3824043567151053</v>
+        <v>0.3768758250056056</v>
       </c>
       <c r="J3" t="n">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="K3" t="n">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1503969343054059</v>
+        <v>0.146150654064106</v>
       </c>
       <c r="M3" t="n">
-        <v>5.653716807183946</v>
+        <v>5.670372340119401</v>
       </c>
       <c r="N3" t="n">
-        <v>49.28252410636739</v>
+        <v>49.61313890995076</v>
       </c>
       <c r="O3" t="n">
-        <v>7.020151287997104</v>
+        <v>7.043659482822176</v>
       </c>
       <c r="P3" t="n">
-        <v>347.34434128356</v>
+        <v>347.3996776375024</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -29623,28 +29681,28 @@
         <v>0.043</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3751582539442969</v>
+        <v>0.3692200590945713</v>
       </c>
       <c r="J4" t="n">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="K4" t="n">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1489067164083642</v>
+        <v>0.1441530364515861</v>
       </c>
       <c r="M4" t="n">
-        <v>5.521270109628059</v>
+        <v>5.541202949269336</v>
       </c>
       <c r="N4" t="n">
-        <v>47.99125210394082</v>
+        <v>48.39077213198064</v>
       </c>
       <c r="O4" t="n">
-        <v>6.927571876490407</v>
+        <v>6.956347614372117</v>
       </c>
       <c r="P4" t="n">
-        <v>344.6894480871663</v>
+        <v>344.7488848543316</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -29701,28 +29759,28 @@
         <v>0.031</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4432215307464309</v>
+        <v>0.4363696106596866</v>
       </c>
       <c r="J5" t="n">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="K5" t="n">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="L5" t="n">
-        <v>0.132389745541732</v>
+        <v>0.1283611188195767</v>
       </c>
       <c r="M5" t="n">
-        <v>7.150263992829651</v>
+        <v>7.172994311137831</v>
       </c>
       <c r="N5" t="n">
-        <v>76.80371376180702</v>
+        <v>77.30930242760316</v>
       </c>
       <c r="O5" t="n">
-        <v>8.763772804095678</v>
+        <v>8.792570865657163</v>
       </c>
       <c r="P5" t="n">
-        <v>340.6528475228483</v>
+        <v>340.7214299774724</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -29779,28 +29837,28 @@
         <v>0.0508</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3755270251006755</v>
+        <v>0.3702337228015797</v>
       </c>
       <c r="J6" t="n">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="K6" t="n">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1049468851283002</v>
+        <v>0.1021925773758652</v>
       </c>
       <c r="M6" t="n">
-        <v>6.791874568751255</v>
+        <v>6.806003497258156</v>
       </c>
       <c r="N6" t="n">
-        <v>71.75164159149364</v>
+        <v>72.00048877545294</v>
       </c>
       <c r="O6" t="n">
-        <v>8.470634072576482</v>
+        <v>8.485310175559462</v>
       </c>
       <c r="P6" t="n">
-        <v>324.6695143281843</v>
+        <v>324.7224962164935</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -29857,28 +29915,28 @@
         <v>0.0368</v>
       </c>
       <c r="I7" t="n">
-        <v>0.206687320363904</v>
+        <v>0.2020915195049608</v>
       </c>
       <c r="J7" t="n">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="K7" t="n">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02854155350823961</v>
+        <v>0.02734176528694843</v>
       </c>
       <c r="M7" t="n">
-        <v>7.314164866568136</v>
+        <v>7.323438244257384</v>
       </c>
       <c r="N7" t="n">
-        <v>86.74500634511601</v>
+        <v>86.86594594419248</v>
       </c>
       <c r="O7" t="n">
-        <v>9.313699927800767</v>
+        <v>9.320190231116127</v>
       </c>
       <c r="P7" t="n">
-        <v>330.6205079256414</v>
+        <v>330.6665083605384</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -29935,28 +29993,28 @@
         <v>0.0357</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2474221353203907</v>
+        <v>0.2437002015657864</v>
       </c>
       <c r="J8" t="n">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="K8" t="n">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1219479446366729</v>
+        <v>0.1184055880487822</v>
       </c>
       <c r="M8" t="n">
-        <v>3.793018443681851</v>
+        <v>3.808364781807478</v>
       </c>
       <c r="N8" t="n">
-        <v>26.29620477393376</v>
+        <v>26.43796747937771</v>
       </c>
       <c r="O8" t="n">
-        <v>5.127982524729756</v>
+        <v>5.141786409350131</v>
       </c>
       <c r="P8" t="n">
-        <v>348.4369775070269</v>
+        <v>348.4742312037437</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -30013,28 +30071,28 @@
         <v>0.0322</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1747501586718517</v>
+        <v>0.1744714144485932</v>
       </c>
       <c r="J9" t="n">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="K9" t="n">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0386036551951241</v>
+        <v>0.03864123771010164</v>
       </c>
       <c r="M9" t="n">
-        <v>4.753129996549112</v>
+        <v>4.745138812242728</v>
       </c>
       <c r="N9" t="n">
-        <v>45.3711083986882</v>
+        <v>45.2796104302972</v>
       </c>
       <c r="O9" t="n">
-        <v>6.735807924717584</v>
+        <v>6.729012589548128</v>
       </c>
       <c r="P9" t="n">
-        <v>365.3660228945072</v>
+        <v>365.3688129099775</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -30091,28 +30149,28 @@
         <v>0.0257</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1270476113395989</v>
+        <v>0.1255690638184467</v>
       </c>
       <c r="J10" t="n">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="K10" t="n">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0181950054435146</v>
+        <v>0.01784504859280711</v>
       </c>
       <c r="M10" t="n">
-        <v>5.581529383052088</v>
+        <v>5.579896694171394</v>
       </c>
       <c r="N10" t="n">
-        <v>51.96085017796307</v>
+        <v>51.88564810019619</v>
       </c>
       <c r="O10" t="n">
-        <v>7.208387488056054</v>
+        <v>7.203169309421804</v>
       </c>
       <c r="P10" t="n">
-        <v>382.1051935213328</v>
+        <v>382.1199926458111</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -30173,28 +30231,28 @@
         <v>0.0708</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6178823232317071</v>
+        <v>0.6135641703185393</v>
       </c>
       <c r="J11" t="n">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="K11" t="n">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3493717515707847</v>
+        <v>0.3457452936900579</v>
       </c>
       <c r="M11" t="n">
-        <v>5.073639787626837</v>
+        <v>5.08684233455859</v>
       </c>
       <c r="N11" t="n">
-        <v>42.41572184857839</v>
+        <v>42.59221411314059</v>
       </c>
       <c r="O11" t="n">
-        <v>6.512735358401906</v>
+        <v>6.526271072606515</v>
       </c>
       <c r="P11" t="n">
-        <v>328.6752682580149</v>
+        <v>328.7184896503367</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -30251,28 +30309,28 @@
         <v>0.07340000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6489616116711612</v>
+        <v>0.6457694121396005</v>
       </c>
       <c r="J12" t="n">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="K12" t="n">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="L12" t="n">
-        <v>0.4185762262029216</v>
+        <v>0.416204766506119</v>
       </c>
       <c r="M12" t="n">
-        <v>4.726739792995055</v>
+        <v>4.735020642671312</v>
       </c>
       <c r="N12" t="n">
-        <v>34.90008103387724</v>
+        <v>34.97261388245799</v>
       </c>
       <c r="O12" t="n">
-        <v>5.907629053510151</v>
+        <v>5.913764780785417</v>
       </c>
       <c r="P12" t="n">
-        <v>339.6958713880879</v>
+        <v>339.727822852313</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -30329,28 +30387,28 @@
         <v>0.0422</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5469106112055644</v>
+        <v>0.5444408432842165</v>
       </c>
       <c r="J13" t="n">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="K13" t="n">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="L13" t="n">
-        <v>0.3788404181934857</v>
+        <v>0.3770146856051046</v>
       </c>
       <c r="M13" t="n">
-        <v>4.255122107599439</v>
+        <v>4.260436624809711</v>
       </c>
       <c r="N13" t="n">
-        <v>29.2583461518905</v>
+        <v>29.28468759531866</v>
       </c>
       <c r="O13" t="n">
-        <v>5.409098460177121</v>
+        <v>5.41153283232382</v>
       </c>
       <c r="P13" t="n">
-        <v>345.8063448427328</v>
+        <v>345.8310653217013</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -30388,7 +30446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N490"/>
+  <dimension ref="A1:N491"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65671,6 +65729,78 @@
         </is>
       </c>
     </row>
+    <row r="491">
+      <c r="A491" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-23 22:17:42+00:00</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>-34.96409479006482,173.6415897784465</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>-34.964535565182615,173.64231566527275</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>-34.9649453828556,173.64307265947392</t>
+        </is>
+      </c>
+      <c r="E491" t="inlineStr">
+        <is>
+          <t>-34.96533183827498,173.64387224972674</t>
+        </is>
+      </c>
+      <c r="F491" t="inlineStr">
+        <is>
+          <t>-34.9656913506996,173.64469886998467</t>
+        </is>
+      </c>
+      <c r="G491" t="inlineStr">
+        <is>
+          <t>-34.96591126869864,173.6456226597303</t>
+        </is>
+      </c>
+      <c r="H491" t="inlineStr">
+        <is>
+          <t>-34.9657493904601,173.64658821791193</t>
+        </is>
+      </c>
+      <c r="I491" t="inlineStr">
+        <is>
+          <t>-34.96550213175956,173.64748177138353</t>
+        </is>
+      </c>
+      <c r="J491" t="inlineStr">
+        <is>
+          <t>-34.96537539128092,173.64838115592462</t>
+        </is>
+      </c>
+      <c r="K491" t="inlineStr">
+        <is>
+          <t>-34.965823205499895,173.6492714380596</t>
+        </is>
+      </c>
+      <c r="L491" t="inlineStr">
+        <is>
+          <t>-34.96571585206991,173.65021152234448</t>
+        </is>
+      </c>
+      <c r="M491" t="inlineStr">
+        <is>
+          <t>-34.965347570312446,173.65102541306706</t>
+        </is>
+      </c>
+      <c r="N491" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0037/nzd0037.xlsx
+++ b/data/nzd0037/nzd0037.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N491"/>
+  <dimension ref="A1:N495"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24020,6 +24020,198 @@
       <c r="N491" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-28 22:17:16+00:00</t>
+        </is>
+      </c>
+      <c r="B492" t="n">
+        <v>353.54</v>
+      </c>
+      <c r="C492" t="n">
+        <v>345.59</v>
+      </c>
+      <c r="D492" t="n">
+        <v>341.13</v>
+      </c>
+      <c r="E492" t="n">
+        <v>337.41</v>
+      </c>
+      <c r="F492" t="n">
+        <v>321.46</v>
+      </c>
+      <c r="G492" t="n">
+        <v>327.69</v>
+      </c>
+      <c r="H492" t="n">
+        <v>344.4</v>
+      </c>
+      <c r="I492" t="n">
+        <v>370.29</v>
+      </c>
+      <c r="J492" t="n">
+        <v>381.05</v>
+      </c>
+      <c r="K492" t="n">
+        <v>334.95</v>
+      </c>
+      <c r="L492" t="n">
+        <v>348.63</v>
+      </c>
+      <c r="M492" t="n">
+        <v>354.83</v>
+      </c>
+      <c r="N492" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-13 22:17:10+00:00</t>
+        </is>
+      </c>
+      <c r="B493" t="n">
+        <v>353.06</v>
+      </c>
+      <c r="C493" t="n">
+        <v>344.88</v>
+      </c>
+      <c r="D493" t="n">
+        <v>339.47</v>
+      </c>
+      <c r="E493" t="n">
+        <v>336.27</v>
+      </c>
+      <c r="F493" t="n">
+        <v>321.72</v>
+      </c>
+      <c r="G493" t="n">
+        <v>328.38</v>
+      </c>
+      <c r="H493" t="n">
+        <v>343.12</v>
+      </c>
+      <c r="I493" t="n">
+        <v>372.63</v>
+      </c>
+      <c r="J493" t="n">
+        <v>378.92</v>
+      </c>
+      <c r="K493" t="n">
+        <v>333.49</v>
+      </c>
+      <c r="L493" t="n">
+        <v>347.87</v>
+      </c>
+      <c r="M493" t="n">
+        <v>353.74</v>
+      </c>
+      <c r="N493" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:11:11+00:00</t>
+        </is>
+      </c>
+      <c r="B494" t="n">
+        <v>352.79</v>
+      </c>
+      <c r="C494" t="n">
+        <v>344.5</v>
+      </c>
+      <c r="D494" t="n">
+        <v>339.82</v>
+      </c>
+      <c r="E494" t="n">
+        <v>336.28</v>
+      </c>
+      <c r="F494" t="n">
+        <v>322.55</v>
+      </c>
+      <c r="G494" t="n">
+        <v>329.65</v>
+      </c>
+      <c r="H494" t="n">
+        <v>343.48</v>
+      </c>
+      <c r="I494" t="n">
+        <v>371.38</v>
+      </c>
+      <c r="J494" t="n">
+        <v>379.58</v>
+      </c>
+      <c r="K494" t="n">
+        <v>333.09</v>
+      </c>
+      <c r="L494" t="n">
+        <v>347.87</v>
+      </c>
+      <c r="M494" t="n">
+        <v>354.11</v>
+      </c>
+      <c r="N494" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:17:21+00:00</t>
+        </is>
+      </c>
+      <c r="B495" t="n">
+        <v>352.3</v>
+      </c>
+      <c r="C495" t="n">
+        <v>344</v>
+      </c>
+      <c r="D495" t="n">
+        <v>339.86</v>
+      </c>
+      <c r="E495" t="n">
+        <v>336.14</v>
+      </c>
+      <c r="F495" t="n">
+        <v>321.26</v>
+      </c>
+      <c r="G495" t="n">
+        <v>327.73</v>
+      </c>
+      <c r="H495" t="n">
+        <v>344.41</v>
+      </c>
+      <c r="I495" t="n">
+        <v>367.42</v>
+      </c>
+      <c r="J495" t="n">
+        <v>377.2</v>
+      </c>
+      <c r="K495" t="n">
+        <v>332.98</v>
+      </c>
+      <c r="L495" t="n">
+        <v>347.4</v>
+      </c>
+      <c r="M495" t="n">
+        <v>353.48</v>
+      </c>
+      <c r="N495" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -24034,7 +24226,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B532"/>
+  <dimension ref="A1:B536"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29357,6 +29549,46 @@
       </c>
       <c r="B532" t="n">
         <v>0.84</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>2026-03-28 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B533" t="n">
+        <v>-0.59</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>2026-04-13 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B534" t="n">
+        <v>-0.58</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B535" t="n">
+        <v>-0.51</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B536" t="n">
+        <v>0.8</v>
       </c>
     </row>
   </sheetData>
@@ -29525,28 +29757,28 @@
         <v>0.0529</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3033970214221905</v>
+        <v>0.2861935146166086</v>
       </c>
       <c r="J2" t="n">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="K2" t="n">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="L2" t="n">
-        <v>0.09250033832559956</v>
+        <v>0.08301515160837625</v>
       </c>
       <c r="M2" t="n">
-        <v>5.900113416724663</v>
+        <v>5.939933073718664</v>
       </c>
       <c r="N2" t="n">
-        <v>53.99399149559843</v>
+        <v>54.58686486530097</v>
       </c>
       <c r="O2" t="n">
-        <v>7.348060390034804</v>
+        <v>7.388292418773161</v>
       </c>
       <c r="P2" t="n">
-        <v>356.2316518092962</v>
+        <v>356.4056053715632</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -29603,28 +29835,28 @@
         <v>0.0581</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3768758250056056</v>
+        <v>0.3576945617296007</v>
       </c>
       <c r="J3" t="n">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="K3" t="n">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="L3" t="n">
-        <v>0.146150654064106</v>
+        <v>0.1326096467108308</v>
       </c>
       <c r="M3" t="n">
-        <v>5.670372340119401</v>
+        <v>5.722934266399988</v>
       </c>
       <c r="N3" t="n">
-        <v>49.61313890995076</v>
+        <v>50.49262226280069</v>
       </c>
       <c r="O3" t="n">
-        <v>7.043659482822176</v>
+        <v>7.105816087037484</v>
       </c>
       <c r="P3" t="n">
-        <v>347.3996776375024</v>
+        <v>347.5936308144105</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -29681,28 +29913,28 @@
         <v>0.043</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3692200590945713</v>
+        <v>0.3472963045999998</v>
       </c>
       <c r="J4" t="n">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="K4" t="n">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1441530364515861</v>
+        <v>0.1277831220286282</v>
       </c>
       <c r="M4" t="n">
-        <v>5.541202949269336</v>
+        <v>5.611562131691458</v>
       </c>
       <c r="N4" t="n">
-        <v>48.39077213198064</v>
+        <v>49.67239465264711</v>
       </c>
       <c r="O4" t="n">
-        <v>6.956347614372117</v>
+        <v>7.047864545566062</v>
       </c>
       <c r="P4" t="n">
-        <v>344.7488848543316</v>
+        <v>344.9705671532597</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -29759,28 +29991,28 @@
         <v>0.031</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4363696106596866</v>
+        <v>0.4124733394141274</v>
       </c>
       <c r="J5" t="n">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="K5" t="n">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1283611188195767</v>
+        <v>0.1154208377019774</v>
       </c>
       <c r="M5" t="n">
-        <v>7.172994311137831</v>
+        <v>7.244365050052289</v>
       </c>
       <c r="N5" t="n">
-        <v>77.30930242760316</v>
+        <v>78.66979699796876</v>
       </c>
       <c r="O5" t="n">
-        <v>8.792570865657163</v>
+        <v>8.869599596259617</v>
       </c>
       <c r="P5" t="n">
-        <v>340.7214299774724</v>
+        <v>340.9630559047538</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -29837,28 +30069,28 @@
         <v>0.0508</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3702337228015797</v>
+        <v>0.3508441364881572</v>
       </c>
       <c r="J6" t="n">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="K6" t="n">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1021925773758652</v>
+        <v>0.09265614180331005</v>
       </c>
       <c r="M6" t="n">
-        <v>6.806003497258156</v>
+        <v>6.853819364937802</v>
       </c>
       <c r="N6" t="n">
-        <v>72.00048877545294</v>
+        <v>72.72603630140674</v>
       </c>
       <c r="O6" t="n">
-        <v>8.485310175559462</v>
+        <v>8.527956162024212</v>
       </c>
       <c r="P6" t="n">
-        <v>324.7224962164935</v>
+        <v>324.9185452526148</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -29915,28 +30147,28 @@
         <v>0.0368</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2020915195049608</v>
+        <v>0.190480409940746</v>
       </c>
       <c r="J7" t="n">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="K7" t="n">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02734176528694843</v>
+        <v>0.02464493676781365</v>
       </c>
       <c r="M7" t="n">
-        <v>7.323438244257384</v>
+        <v>7.324566197902626</v>
       </c>
       <c r="N7" t="n">
-        <v>86.86594594419248</v>
+        <v>86.63621093954113</v>
       </c>
       <c r="O7" t="n">
-        <v>9.320190231116127</v>
+        <v>9.307857483843483</v>
       </c>
       <c r="P7" t="n">
-        <v>330.6665083605384</v>
+        <v>330.7839058657045</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -29993,28 +30225,28 @@
         <v>0.0357</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2437002015657864</v>
+        <v>0.2269192092148231</v>
       </c>
       <c r="J8" t="n">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="K8" t="n">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1184055880487822</v>
+        <v>0.1024928682604072</v>
       </c>
       <c r="M8" t="n">
-        <v>3.808364781807478</v>
+        <v>3.882248843746784</v>
       </c>
       <c r="N8" t="n">
-        <v>26.43796747937771</v>
+        <v>27.20511495786546</v>
       </c>
       <c r="O8" t="n">
-        <v>5.141786409350131</v>
+        <v>5.215852275310858</v>
       </c>
       <c r="P8" t="n">
-        <v>348.4742312037437</v>
+        <v>348.6439075576823</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -30071,28 +30303,28 @@
         <v>0.0322</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1744714144485932</v>
+        <v>0.1750740408261347</v>
       </c>
       <c r="J9" t="n">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="K9" t="n">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03864123771010164</v>
+        <v>0.03952037406732178</v>
       </c>
       <c r="M9" t="n">
-        <v>4.745138812242728</v>
+        <v>4.720047165328132</v>
       </c>
       <c r="N9" t="n">
-        <v>45.2796104302972</v>
+        <v>44.94427745643172</v>
       </c>
       <c r="O9" t="n">
-        <v>6.729012589548128</v>
+        <v>6.704049332786247</v>
       </c>
       <c r="P9" t="n">
-        <v>365.3688129099775</v>
+        <v>365.3627300578599</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -30149,28 +30381,28 @@
         <v>0.0257</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1255690638184467</v>
+        <v>0.1160869652990959</v>
       </c>
       <c r="J10" t="n">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="K10" t="n">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01784504859280711</v>
+        <v>0.01545584476736195</v>
       </c>
       <c r="M10" t="n">
-        <v>5.579896694171394</v>
+        <v>5.596024363488199</v>
       </c>
       <c r="N10" t="n">
-        <v>51.88564810019619</v>
+        <v>51.79324823187259</v>
       </c>
       <c r="O10" t="n">
-        <v>7.203169309421804</v>
+        <v>7.19675261710951</v>
       </c>
       <c r="P10" t="n">
-        <v>382.1199926458111</v>
+        <v>382.2158893028834</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -30231,28 +30463,28 @@
         <v>0.0708</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6135641703185393</v>
+        <v>0.5962565835647112</v>
       </c>
       <c r="J11" t="n">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="K11" t="n">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3457452936900579</v>
+        <v>0.3313100014210676</v>
       </c>
       <c r="M11" t="n">
-        <v>5.08684233455859</v>
+        <v>5.13893399334946</v>
       </c>
       <c r="N11" t="n">
-        <v>42.59221411314059</v>
+        <v>43.29327472033655</v>
       </c>
       <c r="O11" t="n">
-        <v>6.526271072606515</v>
+        <v>6.579762512457159</v>
       </c>
       <c r="P11" t="n">
-        <v>328.7184896503367</v>
+        <v>328.8935015743904</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -30309,28 +30541,28 @@
         <v>0.07340000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6457694121396005</v>
+        <v>0.6321502632162062</v>
       </c>
       <c r="J12" t="n">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="K12" t="n">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="L12" t="n">
-        <v>0.416204766506119</v>
+        <v>0.4055850128699302</v>
       </c>
       <c r="M12" t="n">
-        <v>4.735020642671312</v>
+        <v>4.772446087923449</v>
       </c>
       <c r="N12" t="n">
-        <v>34.97261388245799</v>
+        <v>35.33558451798977</v>
       </c>
       <c r="O12" t="n">
-        <v>5.913764780785417</v>
+        <v>5.944374190609956</v>
       </c>
       <c r="P12" t="n">
-        <v>339.727822852313</v>
+        <v>339.8655350255482</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -30387,28 +30619,28 @@
         <v>0.0422</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5444408432842165</v>
+        <v>0.534892171885845</v>
       </c>
       <c r="J13" t="n">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="K13" t="n">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="L13" t="n">
-        <v>0.3770146856051046</v>
+        <v>0.3702052998333529</v>
       </c>
       <c r="M13" t="n">
-        <v>4.260436624809711</v>
+        <v>4.27959379480504</v>
       </c>
       <c r="N13" t="n">
-        <v>29.28468759531866</v>
+        <v>29.36653018566265</v>
       </c>
       <c r="O13" t="n">
-        <v>5.41153283232382</v>
+        <v>5.419089424032662</v>
       </c>
       <c r="P13" t="n">
-        <v>345.8310653217013</v>
+        <v>345.9276213594802</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -30446,7 +30678,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N491"/>
+  <dimension ref="A1:N495"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65801,6 +66033,294 @@
         </is>
       </c>
     </row>
+    <row r="492">
+      <c r="A492" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-28 22:17:16+00:00</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>-34.96407669435308,173.6416027460596</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>-34.96451467351359,173.64233063642703</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>-34.96492833153629,173.64308409394323</t>
+        </is>
+      </c>
+      <c r="E492" t="inlineStr">
+        <is>
+          <t>-34.96530624441105,173.6438853486865</t>
+        </is>
+      </c>
+      <c r="F492" t="inlineStr">
+        <is>
+          <t>-34.96568450801215,173.6447016440398</t>
+        </is>
+      </c>
+      <c r="G492" t="inlineStr">
+        <is>
+          <t>-34.96587833207856,173.64562977554658</t>
+        </is>
+      </c>
+      <c r="H492" t="inlineStr">
+        <is>
+          <t>-34.96575642353457,173.64658829244632</t>
+        </is>
+      </c>
+      <c r="I492" t="inlineStr">
+        <is>
+          <t>-34.96549284996226,173.64748137202056</t>
+        </is>
+      </c>
+      <c r="J492" t="inlineStr">
+        <is>
+          <t>-34.965380080137614,173.64838117862072</t>
+        </is>
+      </c>
+      <c r="K492" t="inlineStr">
+        <is>
+          <t>-34.96581157734044,173.64927180403174</t>
+        </is>
+      </c>
+      <c r="L492" t="inlineStr">
+        <is>
+          <t>-34.96571444047946,173.65021116014879</t>
+        </is>
+      </c>
+      <c r="M492" t="inlineStr">
+        <is>
+          <t>-34.965339139341275,173.65102042491802</t>
+        </is>
+      </c>
+      <c r="N492" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-13 22:17:10+00:00</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>-34.964080422225145,173.64160007462044</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>-34.964520187671766,173.6423266849335</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>-34.96494143579104,173.6430753063422</t>
+        </is>
+      </c>
+      <c r="E493" t="inlineStr">
+        <is>
+          <t>-34.96531571746475,173.64388050037115</t>
+        </is>
+      </c>
+      <c r="F493" t="inlineStr">
+        <is>
+          <t>-34.965682284138715,173.64470254560766</t>
+        </is>
+      </c>
+      <c r="G493" t="inlineStr">
+        <is>
+          <t>-34.965872206399816,173.64563109897273</t>
+        </is>
+      </c>
+      <c r="H493" t="inlineStr">
+        <is>
+          <t>-34.965767964990114,173.6465884147592</t>
+        </is>
+      </c>
+      <c r="I493" t="inlineStr">
+        <is>
+          <t>-34.965471763160586,173.6474804647303</t>
+        </is>
+      </c>
+      <c r="J493" t="inlineStr">
+        <is>
+          <t>-34.965399286415945,173.64838127158754</t>
+        </is>
+      </c>
+      <c r="K493" t="inlineStr">
+        <is>
+          <t>-34.965824737892994,173.64927138983072</t>
+        </is>
+      </c>
+      <c r="L493" t="inlineStr">
+        <is>
+          <t>-34.965721145534104,173.65021288057852</t>
+        </is>
+      </c>
+      <c r="M493" t="inlineStr">
+        <is>
+          <t>-34.965347975647596,173.65102565288194</t>
+        </is>
+      </c>
+      <c r="N493" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:11:11+00:00</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>-34.964082519153145,173.64159857193584</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>-34.9645231389113,173.64232457004942</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>-34.96493867284581,173.6430771591499</t>
+        </is>
+      </c>
+      <c r="E494" t="inlineStr">
+        <is>
+          <t>-34.9653156343678,173.64388054290026</t>
+        </is>
+      </c>
+      <c r="F494" t="inlineStr">
+        <is>
+          <t>-34.9656751848504,173.6447054236892</t>
+        </is>
+      </c>
+      <c r="G494" t="inlineStr">
+        <is>
+          <t>-34.96586093159979,173.64563353484354</t>
+        </is>
+      </c>
+      <c r="H494" t="inlineStr">
+        <is>
+          <t>-34.96576471895573,173.6465883803587</t>
+        </is>
+      </c>
+      <c r="I494" t="inlineStr">
+        <is>
+          <t>-34.965483027477724,173.64748094939384</t>
+        </is>
+      </c>
+      <c r="J494" t="inlineStr">
+        <is>
+          <t>-34.96539333517478,173.64838124278089</t>
+        </is>
+      </c>
+      <c r="K494" t="inlineStr">
+        <is>
+          <t>-34.965828343523825,173.64927127635096</t>
+        </is>
+      </c>
+      <c r="L494" t="inlineStr">
+        <is>
+          <t>-34.965721145534104,173.65021288057852</t>
+        </is>
+      </c>
+      <c r="M494" t="inlineStr">
+        <is>
+          <t>-34.96534497616749,173.65102387825186</t>
+        </is>
+      </c>
+      <c r="N494" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:17:21+00:00</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>-34.96408632468911,173.6415958448413</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>-34.96452702212115,173.642321787307</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>-34.964938357080655,173.64307737089933</t>
+        </is>
+      </c>
+      <c r="E495" t="inlineStr">
+        <is>
+          <t>-34.96531679772525,173.64387994749302</t>
+        </is>
+      </c>
+      <c r="F495" t="inlineStr">
+        <is>
+          <t>-34.96568621868401,173.64470095052607</t>
+        </is>
+      </c>
+      <c r="G495" t="inlineStr">
+        <is>
+          <t>-34.96587797696674,173.64562985226692</t>
+        </is>
+      </c>
+      <c r="H495" t="inlineStr">
+        <is>
+          <t>-34.965756333366954,173.64658829149076</t>
+        </is>
+      </c>
+      <c r="I495" t="inlineStr">
+        <is>
+          <t>-34.9655187128343,173.6474824848089</t>
+        </is>
+      </c>
+      <c r="J495" t="inlineStr">
+        <is>
+          <t>-34.96541479571108,173.6483813466594</t>
+        </is>
+      </c>
+      <c r="K495" t="inlineStr">
+        <is>
+          <t>-34.9658293350723,173.64927124514404</t>
+        </is>
+      </c>
+      <c r="L495" t="inlineStr">
+        <is>
+          <t>-34.96572529208105,173.65021394452864</t>
+        </is>
+      </c>
+      <c r="M495" t="inlineStr">
+        <is>
+          <t>-34.96535008339035,173.6510268999194</t>
+        </is>
+      </c>
+      <c r="N495" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0037/nzd0037.xlsx
+++ b/data/nzd0037/nzd0037.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N495"/>
+  <dimension ref="A1:N497"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24210,6 +24210,102 @@
         <v>353.48</v>
       </c>
       <c r="N495" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:17:05+00:00</t>
+        </is>
+      </c>
+      <c r="B496" t="n">
+        <v>352.06</v>
+      </c>
+      <c r="C496" t="n">
+        <v>343.64</v>
+      </c>
+      <c r="D496" t="n">
+        <v>339.5</v>
+      </c>
+      <c r="E496" t="n">
+        <v>335.85</v>
+      </c>
+      <c r="F496" t="n">
+        <v>321.01</v>
+      </c>
+      <c r="G496" t="n">
+        <v>327.4</v>
+      </c>
+      <c r="H496" t="n">
+        <v>344.19</v>
+      </c>
+      <c r="I496" t="n">
+        <v>367.42</v>
+      </c>
+      <c r="J496" t="n">
+        <v>376.89</v>
+      </c>
+      <c r="K496" t="n">
+        <v>333.7</v>
+      </c>
+      <c r="L496" t="n">
+        <v>348.38</v>
+      </c>
+      <c r="M496" t="n">
+        <v>354.23</v>
+      </c>
+      <c r="N496" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:49+00:00</t>
+        </is>
+      </c>
+      <c r="B497" t="n">
+        <v>352.74</v>
+      </c>
+      <c r="C497" t="n">
+        <v>344.48</v>
+      </c>
+      <c r="D497" t="n">
+        <v>340.46</v>
+      </c>
+      <c r="E497" t="n">
+        <v>336.06</v>
+      </c>
+      <c r="F497" t="n">
+        <v>321.73</v>
+      </c>
+      <c r="G497" t="n">
+        <v>328.2</v>
+      </c>
+      <c r="H497" t="n">
+        <v>344.75</v>
+      </c>
+      <c r="I497" t="n">
+        <v>364.64</v>
+      </c>
+      <c r="J497" t="n">
+        <v>375.9</v>
+      </c>
+      <c r="K497" t="n">
+        <v>334.38</v>
+      </c>
+      <c r="L497" t="n">
+        <v>349.21</v>
+      </c>
+      <c r="M497" t="n">
+        <v>354.41</v>
+      </c>
+      <c r="N497" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -24226,7 +24322,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B536"/>
+  <dimension ref="A1:B538"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29589,6 +29685,26 @@
       </c>
       <c r="B536" t="n">
         <v>0.8</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B537" t="n">
+        <v>-0.34</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B538" t="n">
+        <v>0.09</v>
       </c>
     </row>
   </sheetData>
@@ -29757,28 +29873,28 @@
         <v>0.0529</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2861935146166086</v>
+        <v>0.2774525285106605</v>
       </c>
       <c r="J2" t="n">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="K2" t="n">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="L2" t="n">
-        <v>0.08301515160837625</v>
+        <v>0.07830954517314892</v>
       </c>
       <c r="M2" t="n">
-        <v>5.939933073718664</v>
+        <v>5.960188249097715</v>
       </c>
       <c r="N2" t="n">
-        <v>54.58686486530097</v>
+        <v>54.9096621110555</v>
       </c>
       <c r="O2" t="n">
-        <v>7.388292418773161</v>
+        <v>7.41010540485461</v>
       </c>
       <c r="P2" t="n">
-        <v>356.4056053715632</v>
+        <v>356.4942819737103</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -29835,28 +29951,28 @@
         <v>0.0581</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3576945617296007</v>
+        <v>0.3478746385996138</v>
       </c>
       <c r="J3" t="n">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="K3" t="n">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1326096467108308</v>
+        <v>0.1257810264447726</v>
       </c>
       <c r="M3" t="n">
-        <v>5.722934266399988</v>
+        <v>5.749844088813082</v>
       </c>
       <c r="N3" t="n">
-        <v>50.49262226280069</v>
+        <v>50.97434320138333</v>
       </c>
       <c r="O3" t="n">
-        <v>7.105816087037484</v>
+        <v>7.139631867357261</v>
       </c>
       <c r="P3" t="n">
-        <v>347.5936308144105</v>
+        <v>347.6932528611306</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -29913,28 +30029,28 @@
         <v>0.043</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3472963045999998</v>
+        <v>0.3365904537919812</v>
       </c>
       <c r="J4" t="n">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="K4" t="n">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1277831220286282</v>
+        <v>0.1201344263498052</v>
       </c>
       <c r="M4" t="n">
-        <v>5.611562131691458</v>
+        <v>5.646094336649846</v>
       </c>
       <c r="N4" t="n">
-        <v>49.67239465264711</v>
+        <v>50.28673566599549</v>
       </c>
       <c r="O4" t="n">
-        <v>7.047864545566062</v>
+        <v>7.091314100080146</v>
       </c>
       <c r="P4" t="n">
-        <v>344.9705671532597</v>
+        <v>345.0791766724193</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -29991,28 +30107,28 @@
         <v>0.031</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4124733394141274</v>
+        <v>0.4004468831614216</v>
       </c>
       <c r="J5" t="n">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="K5" t="n">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1154208377019774</v>
+        <v>0.1090747946227472</v>
       </c>
       <c r="M5" t="n">
-        <v>7.244365050052289</v>
+        <v>7.280977182355099</v>
       </c>
       <c r="N5" t="n">
-        <v>78.66979699796876</v>
+        <v>79.37937703168107</v>
       </c>
       <c r="O5" t="n">
-        <v>8.869599596259617</v>
+        <v>8.909510482157875</v>
       </c>
       <c r="P5" t="n">
-        <v>340.9630559047538</v>
+        <v>341.0850664238737</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -30069,28 +30185,28 @@
         <v>0.0508</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3508441364881572</v>
+        <v>0.3411494406594265</v>
       </c>
       <c r="J6" t="n">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="K6" t="n">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="L6" t="n">
-        <v>0.09265614180331005</v>
+        <v>0.08799664386255446</v>
       </c>
       <c r="M6" t="n">
-        <v>6.853819364937802</v>
+        <v>6.87729547097351</v>
       </c>
       <c r="N6" t="n">
-        <v>72.72603630140674</v>
+        <v>73.10055323591628</v>
       </c>
       <c r="O6" t="n">
-        <v>8.527956162024212</v>
+        <v>8.549886153389195</v>
       </c>
       <c r="P6" t="n">
-        <v>324.9185452526148</v>
+        <v>325.0168973543185</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -30147,28 +30263,28 @@
         <v>0.0368</v>
       </c>
       <c r="I7" t="n">
-        <v>0.190480409940746</v>
+        <v>0.1844251787297296</v>
       </c>
       <c r="J7" t="n">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="K7" t="n">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02464493676781365</v>
+        <v>0.02326285386502236</v>
       </c>
       <c r="M7" t="n">
-        <v>7.324566197902626</v>
+        <v>7.326234410470279</v>
       </c>
       <c r="N7" t="n">
-        <v>86.63621093954113</v>
+        <v>86.54782276183381</v>
       </c>
       <c r="O7" t="n">
-        <v>9.307857483843483</v>
+        <v>9.303108231222177</v>
       </c>
       <c r="P7" t="n">
-        <v>330.7839058657045</v>
+        <v>330.8453343898354</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -30225,28 +30341,28 @@
         <v>0.0357</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2269192092148231</v>
+        <v>0.2192418276698952</v>
       </c>
       <c r="J8" t="n">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="K8" t="n">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1024928682604072</v>
+        <v>0.09573822700172663</v>
       </c>
       <c r="M8" t="n">
-        <v>3.882248843746784</v>
+        <v>3.915743478912563</v>
       </c>
       <c r="N8" t="n">
-        <v>27.20511495786546</v>
+        <v>27.5141834044919</v>
       </c>
       <c r="O8" t="n">
-        <v>5.215852275310858</v>
+        <v>5.245396401082753</v>
       </c>
       <c r="P8" t="n">
-        <v>348.6439075576823</v>
+        <v>348.7217941649679</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -30303,28 +30419,28 @@
         <v>0.0322</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1750740408261347</v>
+        <v>0.1720598610027463</v>
       </c>
       <c r="J9" t="n">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="K9" t="n">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03952037406732178</v>
+        <v>0.03847686787340521</v>
       </c>
       <c r="M9" t="n">
-        <v>4.720047165328132</v>
+        <v>4.71954978710269</v>
       </c>
       <c r="N9" t="n">
-        <v>44.94427745643172</v>
+        <v>44.83530920528464</v>
       </c>
       <c r="O9" t="n">
-        <v>6.704049332786247</v>
+        <v>6.695917353528539</v>
       </c>
       <c r="P9" t="n">
-        <v>365.3627300578599</v>
+        <v>365.3933212771543</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -30381,28 +30497,28 @@
         <v>0.0257</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1160869652990959</v>
+        <v>0.1093976641963524</v>
       </c>
       <c r="J10" t="n">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="K10" t="n">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01545584476736195</v>
+        <v>0.01378154589634339</v>
       </c>
       <c r="M10" t="n">
-        <v>5.596024363488199</v>
+        <v>5.616708818953091</v>
       </c>
       <c r="N10" t="n">
-        <v>51.79324823187259</v>
+        <v>51.90298035015967</v>
       </c>
       <c r="O10" t="n">
-        <v>7.19675261710951</v>
+        <v>7.204372307853036</v>
       </c>
       <c r="P10" t="n">
-        <v>382.2158893028834</v>
+        <v>382.2837580354089</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -30463,28 +30579,28 @@
         <v>0.0708</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5962565835647112</v>
+        <v>0.5881513855537953</v>
       </c>
       <c r="J11" t="n">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="K11" t="n">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3313100014210676</v>
+        <v>0.3247763406058153</v>
       </c>
       <c r="M11" t="n">
-        <v>5.13893399334946</v>
+        <v>5.161759930975633</v>
       </c>
       <c r="N11" t="n">
-        <v>43.29327472033655</v>
+        <v>43.58554942819141</v>
       </c>
       <c r="O11" t="n">
-        <v>6.579762512457159</v>
+        <v>6.601935279006559</v>
       </c>
       <c r="P11" t="n">
-        <v>328.8935015743904</v>
+        <v>328.9757280232942</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -30541,28 +30657,28 @@
         <v>0.07340000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6321502632162062</v>
+        <v>0.6261577638055797</v>
       </c>
       <c r="J12" t="n">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="K12" t="n">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="L12" t="n">
-        <v>0.4055850128699302</v>
+        <v>0.4013044911359196</v>
       </c>
       <c r="M12" t="n">
-        <v>4.772446087923449</v>
+        <v>4.786495944056631</v>
       </c>
       <c r="N12" t="n">
-        <v>35.33558451798977</v>
+        <v>35.4487176026465</v>
       </c>
       <c r="O12" t="n">
-        <v>5.944374190609956</v>
+        <v>5.953882565406081</v>
       </c>
       <c r="P12" t="n">
-        <v>339.8655350255482</v>
+        <v>339.926327046316</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -30619,28 +30735,28 @@
         <v>0.0422</v>
       </c>
       <c r="I13" t="n">
-        <v>0.534892171885845</v>
+        <v>0.5304443132281353</v>
       </c>
       <c r="J13" t="n">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="K13" t="n">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="L13" t="n">
-        <v>0.3702052998333529</v>
+        <v>0.3671816496547942</v>
       </c>
       <c r="M13" t="n">
-        <v>4.27959379480504</v>
+        <v>4.287214145180051</v>
       </c>
       <c r="N13" t="n">
-        <v>29.36653018566265</v>
+        <v>29.38858661564652</v>
       </c>
       <c r="O13" t="n">
-        <v>5.419089424032662</v>
+        <v>5.42112410996525</v>
       </c>
       <c r="P13" t="n">
-        <v>345.9276213594802</v>
+        <v>345.9727453170422</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -30678,7 +30794,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N495"/>
+  <dimension ref="A1:N497"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66321,6 +66437,150 @@
         </is>
       </c>
     </row>
+    <row r="496">
+      <c r="A496" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:17:05+00:00</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>-34.96408818862507,173.64159450912146</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>-34.96452981803222,173.6423197837323</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>-34.96494119896717,173.6430754651543</t>
+        </is>
+      </c>
+      <c r="E496" t="inlineStr">
+        <is>
+          <t>-34.96531920753712,173.64387871414942</t>
+        </is>
+      </c>
+      <c r="F496" t="inlineStr">
+        <is>
+          <t>-34.96568835702384,173.64470008363386</t>
+        </is>
+      </c>
+      <c r="G496" t="inlineStr">
+        <is>
+          <t>-34.96588090663917,173.64562921932392</t>
+        </is>
+      </c>
+      <c r="H496" t="inlineStr">
+        <is>
+          <t>-34.96575831705463,173.64658831251327</t>
+        </is>
+      </c>
+      <c r="I496" t="inlineStr">
+        <is>
+          <t>-34.9655187128343,173.6474824848089</t>
+        </is>
+      </c>
+      <c r="J496" t="inlineStr">
+        <is>
+          <t>-34.96541759099102,173.6483813601898</t>
+        </is>
+      </c>
+      <c r="K496" t="inlineStr">
+        <is>
+          <t>-34.9658228449368,173.64927144940756</t>
+        </is>
+      </c>
+      <c r="L496" t="inlineStr">
+        <is>
+          <t>-34.96571664608954,173.65021172607956</t>
+        </is>
+      </c>
+      <c r="M496" t="inlineStr">
+        <is>
+          <t>-34.965344003363136,173.6510233026962</t>
+        </is>
+      </c>
+      <c r="N496" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:49+00:00</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>-34.96408290747314,173.64159829366088</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>-34.96452329423969,173.64232445873975</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>-34.964933620603055,173.64308054714076</t>
+        </is>
+      </c>
+      <c r="E497" t="inlineStr">
+        <is>
+          <t>-34.96531746250094,173.64387960726035</t>
+        </is>
+      </c>
+      <c r="F497" t="inlineStr">
+        <is>
+          <t>-34.965682198605116,173.64470258028334</t>
+        </is>
+      </c>
+      <c r="G497" t="inlineStr">
+        <is>
+          <t>-34.96587380440296,173.64563075373115</t>
+        </is>
+      </c>
+      <c r="H497" t="inlineStr">
+        <is>
+          <t>-34.965753267667814,173.6465882590014</t>
+        </is>
+      </c>
+      <c r="I497" t="inlineStr">
+        <is>
+          <t>-34.965543764675395,173.64748356270226</t>
+        </is>
+      </c>
+      <c r="J497" t="inlineStr">
+        <is>
+          <t>-34.96542651785273,173.6483814033998</t>
+        </is>
+      </c>
+      <c r="K497" t="inlineStr">
+        <is>
+          <t>-34.96581671536438,173.64927164232313</t>
+        </is>
+      </c>
+      <c r="L497" t="inlineStr">
+        <is>
+          <t>-34.96570932346404,173.65020984718942</t>
+        </is>
+      </c>
+      <c r="M497" t="inlineStr">
+        <is>
+          <t>-34.96534254415659,173.6510224393627</t>
+        </is>
+      </c>
+      <c r="N497" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0037/nzd0037.xlsx
+++ b/data/nzd0037/nzd0037.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N497"/>
+  <dimension ref="A1:N501"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24306,6 +24306,198 @@
         <v>354.41</v>
       </c>
       <c r="N497" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:16:51+00:00</t>
+        </is>
+      </c>
+      <c r="B498" t="n">
+        <v>353.03</v>
+      </c>
+      <c r="C498" t="n">
+        <v>345.75</v>
+      </c>
+      <c r="D498" t="n">
+        <v>342.02</v>
+      </c>
+      <c r="E498" t="n">
+        <v>336.82</v>
+      </c>
+      <c r="F498" t="n">
+        <v>322.29</v>
+      </c>
+      <c r="G498" t="n">
+        <v>328.6</v>
+      </c>
+      <c r="H498" t="n">
+        <v>344.88</v>
+      </c>
+      <c r="I498" t="n">
+        <v>366.89</v>
+      </c>
+      <c r="J498" t="n">
+        <v>376.3</v>
+      </c>
+      <c r="K498" t="n">
+        <v>333.23</v>
+      </c>
+      <c r="L498" t="n">
+        <v>349.57</v>
+      </c>
+      <c r="M498" t="n">
+        <v>354.61</v>
+      </c>
+      <c r="N498" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:30+00:00</t>
+        </is>
+      </c>
+      <c r="B499" t="n">
+        <v>353.75</v>
+      </c>
+      <c r="C499" t="n">
+        <v>347.26</v>
+      </c>
+      <c r="D499" t="n">
+        <v>344.27</v>
+      </c>
+      <c r="E499" t="n">
+        <v>338.66</v>
+      </c>
+      <c r="F499" t="n">
+        <v>323.59</v>
+      </c>
+      <c r="G499" t="n">
+        <v>330.11</v>
+      </c>
+      <c r="H499" t="n">
+        <v>345.8</v>
+      </c>
+      <c r="I499" t="n">
+        <v>368.34</v>
+      </c>
+      <c r="J499" t="n">
+        <v>376.3</v>
+      </c>
+      <c r="K499" t="n">
+        <v>333.44</v>
+      </c>
+      <c r="L499" t="n">
+        <v>350.03</v>
+      </c>
+      <c r="M499" t="n">
+        <v>356</v>
+      </c>
+      <c r="N499" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:16:47+00:00</t>
+        </is>
+      </c>
+      <c r="B500" t="n">
+        <v>354.06</v>
+      </c>
+      <c r="C500" t="n">
+        <v>347.74</v>
+      </c>
+      <c r="D500" t="n">
+        <v>345</v>
+      </c>
+      <c r="E500" t="n">
+        <v>338.87</v>
+      </c>
+      <c r="F500" t="n">
+        <v>324.39</v>
+      </c>
+      <c r="G500" t="n">
+        <v>330.44</v>
+      </c>
+      <c r="H500" t="n">
+        <v>347.38</v>
+      </c>
+      <c r="I500" t="n">
+        <v>368.23</v>
+      </c>
+      <c r="J500" t="n">
+        <v>373.05</v>
+      </c>
+      <c r="K500" t="n">
+        <v>333.18</v>
+      </c>
+      <c r="L500" t="n">
+        <v>349.84</v>
+      </c>
+      <c r="M500" t="n">
+        <v>355.99</v>
+      </c>
+      <c r="N500" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:47+00:00</t>
+        </is>
+      </c>
+      <c r="B501" t="n">
+        <v>354.2</v>
+      </c>
+      <c r="C501" t="n">
+        <v>348.07</v>
+      </c>
+      <c r="D501" t="n">
+        <v>345.5</v>
+      </c>
+      <c r="E501" t="n">
+        <v>339.28</v>
+      </c>
+      <c r="F501" t="n">
+        <v>324.66</v>
+      </c>
+      <c r="G501" t="n">
+        <v>330.83</v>
+      </c>
+      <c r="H501" t="n">
+        <v>349.09</v>
+      </c>
+      <c r="I501" t="n">
+        <v>368.33</v>
+      </c>
+      <c r="J501" t="n">
+        <v>373.7</v>
+      </c>
+      <c r="K501" t="n">
+        <v>333.97</v>
+      </c>
+      <c r="L501" t="n">
+        <v>350.03</v>
+      </c>
+      <c r="M501" t="n">
+        <v>356.47</v>
+      </c>
+      <c r="N501" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -24322,7 +24514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B538"/>
+  <dimension ref="A1:B542"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29705,6 +29897,46 @@
       </c>
       <c r="B538" t="n">
         <v>0.09</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B539" t="n">
+        <v>-0.22</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B540" t="n">
+        <v>-0.54</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B541" t="n">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B542" t="n">
+        <v>0.88</v>
       </c>
     </row>
   </sheetData>
@@ -29873,28 +30105,28 @@
         <v>0.0529</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2774525285106605</v>
+        <v>0.2624275581249933</v>
       </c>
       <c r="J2" t="n">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="K2" t="n">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="L2" t="n">
-        <v>0.07830954517314892</v>
+        <v>0.07077666385279224</v>
       </c>
       <c r="M2" t="n">
-        <v>5.960188249097715</v>
+        <v>5.987207321733137</v>
       </c>
       <c r="N2" t="n">
-        <v>54.9096621110555</v>
+        <v>55.28298709752688</v>
       </c>
       <c r="O2" t="n">
-        <v>7.41010540485461</v>
+        <v>7.435252994856791</v>
       </c>
       <c r="P2" t="n">
-        <v>356.4942819737103</v>
+        <v>356.6474129938049</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -29951,28 +30183,28 @@
         <v>0.0581</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3478746385996138</v>
+        <v>0.3333725782324811</v>
       </c>
       <c r="J3" t="n">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="K3" t="n">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1257810264447726</v>
+        <v>0.1169095100762957</v>
       </c>
       <c r="M3" t="n">
-        <v>5.749844088813082</v>
+        <v>5.777751131776986</v>
       </c>
       <c r="N3" t="n">
-        <v>50.97434320138333</v>
+        <v>51.32839886589968</v>
       </c>
       <c r="O3" t="n">
-        <v>7.139631867357261</v>
+        <v>7.164384053489852</v>
       </c>
       <c r="P3" t="n">
-        <v>347.6932528611306</v>
+        <v>347.8410515974356</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -30029,28 +30261,28 @@
         <v>0.043</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3365904537919812</v>
+        <v>0.321954239880716</v>
       </c>
       <c r="J4" t="n">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="K4" t="n">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1201344263498052</v>
+        <v>0.1111760657993971</v>
       </c>
       <c r="M4" t="n">
-        <v>5.646094336649846</v>
+        <v>5.679451189780375</v>
       </c>
       <c r="N4" t="n">
-        <v>50.28673566599549</v>
+        <v>50.66818399887039</v>
       </c>
       <c r="O4" t="n">
-        <v>7.091314100080146</v>
+        <v>7.118158750608924</v>
       </c>
       <c r="P4" t="n">
-        <v>345.0791766724193</v>
+        <v>345.2283397471501</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -30107,28 +30339,28 @@
         <v>0.031</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4004468831614216</v>
+        <v>0.3806346151201563</v>
       </c>
       <c r="J5" t="n">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="K5" t="n">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1090747946227472</v>
+        <v>0.09951101956842812</v>
       </c>
       <c r="M5" t="n">
-        <v>7.280977182355099</v>
+        <v>7.330282179778374</v>
       </c>
       <c r="N5" t="n">
-        <v>79.37937703168107</v>
+        <v>80.16160246197445</v>
       </c>
       <c r="O5" t="n">
-        <v>8.909510482157875</v>
+        <v>8.953301204693968</v>
       </c>
       <c r="P5" t="n">
-        <v>341.0850664238737</v>
+        <v>341.2869868080607</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -30185,28 +30417,28 @@
         <v>0.0508</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3411494406594265</v>
+        <v>0.3257431294984369</v>
       </c>
       <c r="J6" t="n">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="K6" t="n">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="L6" t="n">
-        <v>0.08799664386255446</v>
+        <v>0.08123584076479562</v>
       </c>
       <c r="M6" t="n">
-        <v>6.87729547097351</v>
+        <v>6.903683030728187</v>
       </c>
       <c r="N6" t="n">
-        <v>73.10055323591628</v>
+        <v>73.37523355219884</v>
       </c>
       <c r="O6" t="n">
-        <v>8.549886153389195</v>
+        <v>8.565934482133216</v>
       </c>
       <c r="P6" t="n">
-        <v>325.0168973543185</v>
+        <v>325.1739115426483</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -30263,28 +30495,28 @@
         <v>0.0368</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1844251787297296</v>
+        <v>0.1758667388271049</v>
       </c>
       <c r="J7" t="n">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="K7" t="n">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02326285386502236</v>
+        <v>0.02148579100897841</v>
       </c>
       <c r="M7" t="n">
-        <v>7.326234410470279</v>
+        <v>7.310985630056646</v>
       </c>
       <c r="N7" t="n">
-        <v>86.54782276183381</v>
+        <v>86.12432126442087</v>
       </c>
       <c r="O7" t="n">
-        <v>9.303108231222177</v>
+        <v>9.280319028159585</v>
       </c>
       <c r="P7" t="n">
-        <v>330.8453343898354</v>
+        <v>330.9325563379709</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -30341,28 +30573,28 @@
         <v>0.0357</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2192418276698952</v>
+        <v>0.2077029119551541</v>
       </c>
       <c r="J8" t="n">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="K8" t="n">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="L8" t="n">
-        <v>0.09573822700172663</v>
+        <v>0.08667931876122648</v>
       </c>
       <c r="M8" t="n">
-        <v>3.915743478912563</v>
+        <v>3.95744222180222</v>
       </c>
       <c r="N8" t="n">
-        <v>27.5141834044919</v>
+        <v>27.79300946742233</v>
       </c>
       <c r="O8" t="n">
-        <v>5.245396401082753</v>
+        <v>5.271907573869474</v>
       </c>
       <c r="P8" t="n">
-        <v>348.7217941649679</v>
+        <v>348.839386596481</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -30419,28 +30651,28 @@
         <v>0.0322</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1720598610027463</v>
+        <v>0.1690070713531236</v>
       </c>
       <c r="J9" t="n">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="K9" t="n">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03847686787340521</v>
+        <v>0.03775295704637582</v>
       </c>
       <c r="M9" t="n">
-        <v>4.71954978710269</v>
+        <v>4.700489256279901</v>
       </c>
       <c r="N9" t="n">
-        <v>44.83530920528464</v>
+        <v>44.51311281658198</v>
       </c>
       <c r="O9" t="n">
-        <v>6.695917353528539</v>
+        <v>6.67181480682595</v>
       </c>
       <c r="P9" t="n">
-        <v>365.3933212771543</v>
+        <v>365.4244322793136</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -30497,28 +30729,28 @@
         <v>0.0257</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1093976641963524</v>
+        <v>0.09408641418287345</v>
       </c>
       <c r="J10" t="n">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="K10" t="n">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01378154589634339</v>
+        <v>0.01023376603978576</v>
       </c>
       <c r="M10" t="n">
-        <v>5.616708818953091</v>
+        <v>5.670436708994379</v>
       </c>
       <c r="N10" t="n">
-        <v>51.90298035015967</v>
+        <v>52.34721558165526</v>
       </c>
       <c r="O10" t="n">
-        <v>7.204372307853036</v>
+        <v>7.235137564805195</v>
       </c>
       <c r="P10" t="n">
-        <v>382.2837580354089</v>
+        <v>382.4398210958254</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -30579,28 +30811,28 @@
         <v>0.0708</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5881513855537953</v>
+        <v>0.5714532584684229</v>
       </c>
       <c r="J11" t="n">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="K11" t="n">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3247763406058153</v>
+        <v>0.3109777975905869</v>
       </c>
       <c r="M11" t="n">
-        <v>5.161759930975633</v>
+        <v>5.210994014577602</v>
       </c>
       <c r="N11" t="n">
-        <v>43.58554942819141</v>
+        <v>44.23926084144485</v>
       </c>
       <c r="O11" t="n">
-        <v>6.601935279006559</v>
+        <v>6.651260094256189</v>
       </c>
       <c r="P11" t="n">
-        <v>328.9757280232942</v>
+        <v>329.1459137585637</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -30657,28 +30889,28 @@
         <v>0.07340000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6261577638055797</v>
+        <v>0.6159999698077765</v>
       </c>
       <c r="J12" t="n">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="K12" t="n">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="L12" t="n">
-        <v>0.4013044911359196</v>
+        <v>0.3949961608550473</v>
       </c>
       <c r="M12" t="n">
-        <v>4.786495944056631</v>
+        <v>4.805112977704716</v>
       </c>
       <c r="N12" t="n">
-        <v>35.4487176026465</v>
+        <v>35.53605717830152</v>
       </c>
       <c r="O12" t="n">
-        <v>5.953882565406081</v>
+        <v>5.96121272714718</v>
       </c>
       <c r="P12" t="n">
-        <v>339.926327046316</v>
+        <v>340.0298543740337</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -30735,28 +30967,28 @@
         <v>0.0422</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5304443132281353</v>
+        <v>0.5238630095889215</v>
       </c>
       <c r="J13" t="n">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="K13" t="n">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="L13" t="n">
-        <v>0.3671816496547942</v>
+        <v>0.3640395022258722</v>
       </c>
       <c r="M13" t="n">
-        <v>4.287214145180051</v>
+        <v>4.289865532696271</v>
       </c>
       <c r="N13" t="n">
-        <v>29.38858661564652</v>
+        <v>29.31296154326225</v>
       </c>
       <c r="O13" t="n">
-        <v>5.42112410996525</v>
+        <v>5.414144580934485</v>
       </c>
       <c r="P13" t="n">
-        <v>345.9727453170422</v>
+        <v>346.0398177447493</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -30794,7 +31026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N497"/>
+  <dimension ref="A1:N501"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66581,6 +66813,294 @@
         </is>
       </c>
     </row>
+    <row r="498">
+      <c r="A498" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:16:51+00:00</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>-34.964080655217124,173.6415999076555</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>-34.96451343088638,173.64233152690434</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>-34.9649213057609,173.64308880536672</t>
+        </is>
+      </c>
+      <c r="E498" t="inlineStr">
+        <is>
+          <t>-34.96531114713185,173.64388283947082</t>
+        </is>
+      </c>
+      <c r="F498" t="inlineStr">
+        <is>
+          <t>-34.96567740872384,173.64470452212154</t>
+        </is>
+      </c>
+      <c r="G498" t="inlineStr">
+        <is>
+          <t>-34.965870253284855,173.64563152093464</t>
+        </is>
+      </c>
+      <c r="H498" t="inlineStr">
+        <is>
+          <t>-34.96575209548873,173.646588246579</t>
+        </is>
+      </c>
+      <c r="I498" t="inlineStr">
+        <is>
+          <t>-34.965523488904736,173.6474826903065</t>
+        </is>
+      </c>
+      <c r="J498" t="inlineStr">
+        <is>
+          <t>-34.96542291103991,173.64838138594124</t>
+        </is>
+      </c>
+      <c r="K498" t="inlineStr">
+        <is>
+          <t>-34.96582708155303,173.64927131606888</t>
+        </is>
+      </c>
+      <c r="L498" t="inlineStr">
+        <is>
+          <t>-34.96570614738549,173.65020903224922</t>
+        </is>
+      </c>
+      <c r="M498" t="inlineStr">
+        <is>
+          <t>-34.96534092281596,173.6510214801033</t>
+        </is>
+      </c>
+      <c r="N498" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:30+00:00</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>-34.96407506340902,173.64160391481417</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>-34.96450170359174,173.64233993078295</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>-34.96490354396834,173.64310071626522</t>
+        </is>
+      </c>
+      <c r="E499" t="inlineStr">
+        <is>
+          <t>-34.965295857290535,173.6438906648205</t>
+        </is>
+      </c>
+      <c r="F499" t="inlineStr">
+        <is>
+          <t>-34.96566628935649,173.64470902995944</t>
+        </is>
+      </c>
+      <c r="G499" t="inlineStr">
+        <is>
+          <t>-34.965856847813946,173.6456344171273</t>
+        </is>
+      </c>
+      <c r="H499" t="inlineStr">
+        <is>
+          <t>-34.96574380006754,173.64658815866665</t>
+        </is>
+      </c>
+      <c r="I499" t="inlineStr">
+        <is>
+          <t>-34.96551042229694,173.6474821280962</t>
+        </is>
+      </c>
+      <c r="J499" t="inlineStr">
+        <is>
+          <t>-34.96542291103991,173.64838138594124</t>
+        </is>
+      </c>
+      <c r="K499" t="inlineStr">
+        <is>
+          <t>-34.96582518859684,173.64927137564575</t>
+        </is>
+      </c>
+      <c r="L499" t="inlineStr">
+        <is>
+          <t>-34.96570208906288,173.65020799093685</t>
+        </is>
+      </c>
+      <c r="M499" t="inlineStr">
+        <is>
+          <t>-34.96532965449844,173.65101481325158</t>
+        </is>
+      </c>
+      <c r="N499" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:16:47+00:00</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>-34.96407265582494,173.6416056401184</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>-34.96449797570988,173.64234260221406</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>-34.964897781253185,173.64310458068897</t>
+        </is>
+      </c>
+      <c r="E500" t="inlineStr">
+        <is>
+          <t>-34.96529411225426,173.64389155793086</t>
+        </is>
+      </c>
+      <c r="F500" t="inlineStr">
+        <is>
+          <t>-34.96565944666879,173.64471180401293</t>
+        </is>
+      </c>
+      <c r="G500" t="inlineStr">
+        <is>
+          <t>-34.96585391814147,173.64563505006996</t>
+        </is>
+      </c>
+      <c r="H500" t="inlineStr">
+        <is>
+          <t>-34.965729553583294,173.64658800768686</t>
+        </is>
+      </c>
+      <c r="I500" t="inlineStr">
+        <is>
+          <t>-34.96551141355684,173.6474821707466</t>
+        </is>
+      </c>
+      <c r="J500" t="inlineStr">
+        <is>
+          <t>-34.96545221639394,173.64838152779242</t>
+        </is>
+      </c>
+      <c r="K500" t="inlineStr">
+        <is>
+          <t>-34.965827532256895,173.6492713018839</t>
+        </is>
+      </c>
+      <c r="L500" t="inlineStr">
+        <is>
+          <t>-34.96570376532656,173.6502084210441</t>
+        </is>
+      </c>
+      <c r="M500" t="inlineStr">
+        <is>
+          <t>-34.965329735565476,173.65101486121452</t>
+        </is>
+      </c>
+      <c r="N500" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:47+00:00</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>-34.9640715685289,173.64160641928802</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>-34.964495412791074,173.6423444388228</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>-34.96489383418791,173.64310722755428</t>
+        </is>
+      </c>
+      <c r="E501" t="inlineStr">
+        <is>
+          <t>-34.96529070527867,173.64389330162248</t>
+        </is>
+      </c>
+      <c r="F501" t="inlineStr">
+        <is>
+          <t>-34.96565713726169,173.64471274025587</t>
+        </is>
+      </c>
+      <c r="G501" t="inlineStr">
+        <is>
+          <t>-34.96585045580128,173.645635798093</t>
+        </is>
+      </c>
+      <c r="H501" t="inlineStr">
+        <is>
+          <t>-34.96571413491993,173.64658784428477</t>
+        </is>
+      </c>
+      <c r="I501" t="inlineStr">
+        <is>
+          <t>-34.96551051241148,173.64748213197348</t>
+        </is>
+      </c>
+      <c r="J501" t="inlineStr">
+        <is>
+          <t>-34.96544635532315,173.64838149942216</t>
+        </is>
+      </c>
+      <c r="K501" t="inlineStr">
+        <is>
+          <t>-34.965820411135994,173.6492715260064</t>
+        </is>
+      </c>
+      <c r="L501" t="inlineStr">
+        <is>
+          <t>-34.96570208906288,173.65020799093685</t>
+        </is>
+      </c>
+      <c r="M501" t="inlineStr">
+        <is>
+          <t>-34.96532584434782,173.65101255899276</t>
+        </is>
+      </c>
+      <c r="N501" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
